--- a/research/traditional_assets/database/data/canada/canada_diversified.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07733139435579917</v>
+        <v>0.07715954116075628</v>
       </c>
       <c r="C2">
-        <v>111.7364457033756</v>
+        <v>110.9965924032694</v>
       </c>
       <c r="D2">
-        <v>109.6964457033756</v>
+        <v>110.2975924032694</v>
       </c>
       <c r="E2">
-        <v>-53</v>
+        <v>-51.659</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.341</v>
       </c>
       <c r="G2">
         <v>2.04</v>
@@ -1451,28 +1451,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06745229999999999</v>
       </c>
       <c r="N2">
-        <v>12.89333333333333</v>
+        <v>12.82588103333333</v>
       </c>
       <c r="O2">
-        <v>3.416733333333333</v>
+        <v>3.398858473833333</v>
       </c>
       <c r="P2">
-        <v>9.476599999999998</v>
+        <v>9.427022559499999</v>
       </c>
       <c r="Q2">
-        <v>13.9166</v>
+        <v>13.8670225595</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07733139435579917</v>
+        <v>0.077565491071471</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.733614112505104</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>191.1474231914009</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07715954116075628</v>
+        <v>0.07698768796571341</v>
       </c>
       <c r="C3">
-        <v>110.9965924032694</v>
+        <v>110.2633640880726</v>
       </c>
       <c r="D3">
-        <v>110.2975924032694</v>
+        <v>110.9053640880726</v>
       </c>
       <c r="E3">
-        <v>-51.659</v>
+        <v>-50.318</v>
       </c>
       <c r="F3">
-        <v>1.341</v>
+        <v>2.682</v>
       </c>
       <c r="G3">
         <v>2.04</v>
@@ -1533,28 +1533,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M3">
-        <v>0.06745229999999999</v>
+        <v>0.1349046</v>
       </c>
       <c r="N3">
-        <v>12.82588103333333</v>
+        <v>12.75842873333333</v>
       </c>
       <c r="O3">
-        <v>3.398858473833333</v>
+        <v>3.380983614333333</v>
       </c>
       <c r="P3">
-        <v>9.427022559499999</v>
+        <v>9.377445118999997</v>
       </c>
       <c r="Q3">
-        <v>13.8670225595</v>
+        <v>13.817445119</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.077565491071471</v>
+        <v>0.07780436527113614</v>
       </c>
       <c r="T3">
-        <v>0.733614112505104</v>
+        <v>0.7391308376705807</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>191.1474231914009</v>
+        <v>95.57371159570046</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07698768796571341</v>
+        <v>0.07681583477067054</v>
       </c>
       <c r="C4">
-        <v>110.2633640880726</v>
+        <v>109.5368708813559</v>
       </c>
       <c r="D4">
-        <v>110.9053640880726</v>
+        <v>111.5198708813559</v>
       </c>
       <c r="E4">
-        <v>-50.318</v>
+        <v>-48.977</v>
       </c>
       <c r="F4">
-        <v>2.682</v>
+        <v>4.023</v>
       </c>
       <c r="G4">
         <v>2.04</v>
@@ -1615,28 +1615,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M4">
-        <v>0.1349046</v>
+        <v>0.2023569</v>
       </c>
       <c r="N4">
-        <v>12.75842873333333</v>
+        <v>12.69097643333333</v>
       </c>
       <c r="O4">
-        <v>3.380983614333333</v>
+        <v>3.363108754833333</v>
       </c>
       <c r="P4">
-        <v>9.377445118999997</v>
+        <v>9.327867678499999</v>
       </c>
       <c r="Q4">
-        <v>13.817445119</v>
+        <v>13.7678676785</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07780436527113614</v>
+        <v>0.07804816471203149</v>
       </c>
       <c r="T4">
-        <v>0.7391308376705807</v>
+        <v>0.7447613097466861</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.57371159570046</v>
+        <v>63.71580773046697</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07681583477067054</v>
+        <v>0.0766439815756277</v>
       </c>
       <c r="C5">
-        <v>109.5368708813559</v>
+        <v>108.8172253609886</v>
       </c>
       <c r="D5">
-        <v>111.5198708813559</v>
+        <v>112.1412253609886</v>
       </c>
       <c r="E5">
-        <v>-48.977</v>
+        <v>-47.636</v>
       </c>
       <c r="F5">
-        <v>4.023</v>
+        <v>5.364</v>
       </c>
       <c r="G5">
         <v>2.04</v>
@@ -1697,28 +1697,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M5">
-        <v>0.2023569</v>
+        <v>0.2698092</v>
       </c>
       <c r="N5">
-        <v>12.69097643333333</v>
+        <v>12.62352413333333</v>
       </c>
       <c r="O5">
-        <v>3.363108754833333</v>
+        <v>3.345233895333333</v>
       </c>
       <c r="P5">
-        <v>9.327867678499999</v>
+        <v>9.278290237999999</v>
       </c>
       <c r="Q5">
-        <v>13.7678676785</v>
+        <v>13.718290238</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07804816471203149</v>
+        <v>0.07829704330794551</v>
       </c>
       <c r="T5">
-        <v>0.7447613097466861</v>
+        <v>0.7505090833243767</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.71580773046697</v>
+        <v>47.78685579785023</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0766439815756277</v>
+        <v>0.07647212838058483</v>
       </c>
       <c r="C6">
-        <v>108.8172253609886</v>
+        <v>108.1045426278956</v>
       </c>
       <c r="D6">
-        <v>112.1412253609886</v>
+        <v>112.7695426278956</v>
       </c>
       <c r="E6">
-        <v>-47.636</v>
+        <v>-46.295</v>
       </c>
       <c r="F6">
-        <v>5.364</v>
+        <v>6.705</v>
       </c>
       <c r="G6">
         <v>2.04</v>
@@ -1779,28 +1779,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M6">
-        <v>0.2698092</v>
+        <v>0.3372615</v>
       </c>
       <c r="N6">
-        <v>12.62352413333333</v>
+        <v>12.55607183333333</v>
       </c>
       <c r="O6">
-        <v>3.345233895333333</v>
+        <v>3.327359035833333</v>
       </c>
       <c r="P6">
-        <v>9.278290237999999</v>
+        <v>9.228712797499998</v>
       </c>
       <c r="Q6">
-        <v>13.718290238</v>
+        <v>13.6687127975</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07829704330794551</v>
+        <v>0.07855116145324718</v>
       </c>
       <c r="T6">
-        <v>0.7505090833243767</v>
+        <v>0.7563778626615979</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.78685579785023</v>
+        <v>38.22948463828018</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07647212838058483</v>
+        <v>0.07630027518554196</v>
       </c>
       <c r="C7">
-        <v>108.1045426278956</v>
+        <v>107.3989403771367</v>
       </c>
       <c r="D7">
-        <v>112.7695426278956</v>
+        <v>113.4049403771367</v>
       </c>
       <c r="E7">
-        <v>-46.295</v>
+        <v>-44.954</v>
       </c>
       <c r="F7">
-        <v>6.705</v>
+        <v>8.046000000000001</v>
       </c>
       <c r="G7">
         <v>2.04</v>
@@ -1861,28 +1861,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M7">
-        <v>0.3372615</v>
+        <v>0.4047138</v>
       </c>
       <c r="N7">
-        <v>12.55607183333333</v>
+        <v>12.48861953333333</v>
       </c>
       <c r="O7">
-        <v>3.327359035833333</v>
+        <v>3.309484176333333</v>
       </c>
       <c r="P7">
-        <v>9.228712797499998</v>
+        <v>9.179135356999998</v>
       </c>
       <c r="Q7">
-        <v>13.6687127975</v>
+        <v>13.619135357</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07855116145324718</v>
+        <v>0.07881068636759783</v>
       </c>
       <c r="T7">
-        <v>0.7563778626615979</v>
+        <v>0.7623715096442917</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.22948463828018</v>
+        <v>31.85790386523348</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07630027518554194</v>
+        <v>0.0761284219904991</v>
       </c>
       <c r="C8">
-        <v>107.3989403771367</v>
+        <v>106.7005389714045</v>
       </c>
       <c r="D8">
-        <v>113.4049403771367</v>
+        <v>114.0475389714045</v>
       </c>
       <c r="E8">
-        <v>-44.954</v>
+        <v>-43.613</v>
       </c>
       <c r="F8">
-        <v>8.045999999999999</v>
+        <v>9.386999999999999</v>
       </c>
       <c r="G8">
         <v>2.04</v>
@@ -1943,28 +1943,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M8">
-        <v>0.4047138</v>
+        <v>0.4721660999999999</v>
       </c>
       <c r="N8">
-        <v>12.48861953333333</v>
+        <v>12.42116723333333</v>
       </c>
       <c r="O8">
-        <v>3.309484176333333</v>
+        <v>3.291609316833333</v>
       </c>
       <c r="P8">
-        <v>9.179135356999998</v>
+        <v>9.129557916499998</v>
       </c>
       <c r="Q8">
-        <v>13.619135357</v>
+        <v>13.5695579165</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07881068636759782</v>
+        <v>0.07907579246290225</v>
       </c>
       <c r="T8">
-        <v>0.7623715096442916</v>
+        <v>0.768494052261022</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.85790386523349</v>
+        <v>27.30677474162871</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07612842199049909</v>
+        <v>0.07595656879545622</v>
       </c>
       <c r="C9">
-        <v>106.7005389714045</v>
+        <v>106.0094615170346</v>
       </c>
       <c r="D9">
-        <v>114.0475389714045</v>
+        <v>114.6974615170346</v>
       </c>
       <c r="E9">
-        <v>-43.613</v>
+        <v>-42.272</v>
       </c>
       <c r="F9">
-        <v>9.387</v>
+        <v>10.728</v>
       </c>
       <c r="G9">
         <v>2.04</v>
@@ -2025,28 +2025,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M9">
-        <v>0.4721661</v>
+        <v>0.5396183999999999</v>
       </c>
       <c r="N9">
-        <v>12.42116723333333</v>
+        <v>12.35371493333333</v>
       </c>
       <c r="O9">
-        <v>3.291609316833333</v>
+        <v>3.273734457333333</v>
       </c>
       <c r="P9">
-        <v>9.129557916499998</v>
+        <v>9.079980475999998</v>
       </c>
       <c r="Q9">
-        <v>13.5695579165</v>
+        <v>13.519980476</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07907579246290225</v>
+        <v>0.07934666173419154</v>
       </c>
       <c r="T9">
-        <v>0.768494052261022</v>
+        <v>0.7747496936302898</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.3067747416287</v>
+        <v>23.89342789892511</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07595656879545622</v>
+        <v>0.07578471560041335</v>
       </c>
       <c r="C10">
-        <v>106.0094615170346</v>
+        <v>105.3258339426293</v>
       </c>
       <c r="D10">
-        <v>114.6974615170346</v>
+        <v>115.3548339426293</v>
       </c>
       <c r="E10">
-        <v>-42.272</v>
+        <v>-40.931</v>
       </c>
       <c r="F10">
-        <v>10.728</v>
+        <v>12.069</v>
       </c>
       <c r="G10">
         <v>2.04</v>
@@ -2107,28 +2107,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M10">
-        <v>0.5396183999999999</v>
+        <v>0.6070707</v>
       </c>
       <c r="N10">
-        <v>12.35371493333333</v>
+        <v>12.28626263333333</v>
       </c>
       <c r="O10">
-        <v>3.273734457333333</v>
+        <v>3.255859597833333</v>
       </c>
       <c r="P10">
-        <v>9.079980475999998</v>
+        <v>9.030403035499997</v>
       </c>
       <c r="Q10">
-        <v>13.519980476</v>
+        <v>13.4704030355</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07934666173419154</v>
+        <v>0.0796234841762784</v>
       </c>
       <c r="T10">
-        <v>0.7747496936302898</v>
+        <v>0.7811428216230579</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.89342789892511</v>
+        <v>21.23860257682232</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07578471560041335</v>
+        <v>0.07561286240537048</v>
       </c>
       <c r="C11">
-        <v>105.3258339426293</v>
+        <v>104.6497850804009</v>
       </c>
       <c r="D11">
-        <v>115.3548339426293</v>
+        <v>116.0197850804009</v>
       </c>
       <c r="E11">
-        <v>-40.931</v>
+        <v>-39.59</v>
       </c>
       <c r="F11">
-        <v>12.069</v>
+        <v>13.41</v>
       </c>
       <c r="G11">
         <v>2.04</v>
@@ -2189,28 +2189,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M11">
-        <v>0.6070707</v>
+        <v>0.6745229999999999</v>
       </c>
       <c r="N11">
-        <v>12.28626263333333</v>
+        <v>12.21881033333333</v>
       </c>
       <c r="O11">
-        <v>3.255859597833333</v>
+        <v>3.237984738333333</v>
       </c>
       <c r="P11">
-        <v>9.030403035499997</v>
+        <v>8.980825594999997</v>
       </c>
       <c r="Q11">
-        <v>13.4704030355</v>
+        <v>13.420825595</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0796234841762784</v>
+        <v>0.07990645822818943</v>
       </c>
       <c r="T11">
-        <v>0.7811428216230579</v>
+        <v>0.7876780191267766</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.23860257682232</v>
+        <v>19.11474231914009</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07561286240537048</v>
+        <v>0.07544100921032762</v>
       </c>
       <c r="C12">
-        <v>104.6497850804009</v>
+        <v>103.9814467503452</v>
       </c>
       <c r="D12">
-        <v>116.0197850804009</v>
+        <v>116.6924467503452</v>
       </c>
       <c r="E12">
-        <v>-39.59</v>
+        <v>-38.249</v>
       </c>
       <c r="F12">
-        <v>13.41</v>
+        <v>14.751</v>
       </c>
       <c r="G12">
         <v>2.04</v>
@@ -2271,28 +2271,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M12">
-        <v>0.674523</v>
+        <v>0.7419752999999999</v>
       </c>
       <c r="N12">
-        <v>12.21881033333333</v>
+        <v>12.15135803333333</v>
       </c>
       <c r="O12">
-        <v>3.237984738333333</v>
+        <v>3.220109878833333</v>
       </c>
       <c r="P12">
-        <v>8.980825594999997</v>
+        <v>8.931248154499999</v>
       </c>
       <c r="Q12">
-        <v>13.420825595</v>
+        <v>13.3712481545</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07990645822818943</v>
+        <v>0.08019579124755911</v>
       </c>
       <c r="T12">
-        <v>0.7876780191267766</v>
+        <v>0.7943600750013654</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.11474231914009</v>
+        <v>17.37703847194554</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07544100921032762</v>
+        <v>0.07526915601528475</v>
       </c>
       <c r="C13">
-        <v>103.9814467503452</v>
+        <v>103.3209538473593</v>
       </c>
       <c r="D13">
-        <v>116.6924467503452</v>
+        <v>117.3729538473593</v>
       </c>
       <c r="E13">
-        <v>-38.249</v>
+        <v>-36.908</v>
       </c>
       <c r="F13">
-        <v>14.751</v>
+        <v>16.092</v>
       </c>
       <c r="G13">
         <v>2.04</v>
@@ -2353,28 +2353,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M13">
-        <v>0.7419752999999999</v>
+        <v>0.8094275999999999</v>
       </c>
       <c r="N13">
-        <v>12.15135803333333</v>
+        <v>12.08390573333333</v>
       </c>
       <c r="O13">
-        <v>3.220109878833333</v>
+        <v>3.202235019333333</v>
       </c>
       <c r="P13">
-        <v>8.931248154499999</v>
+        <v>8.881670713999998</v>
       </c>
       <c r="Q13">
-        <v>13.3712481545</v>
+        <v>13.321670714</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08019579124755911</v>
+        <v>0.08049170001736902</v>
       </c>
       <c r="T13">
-        <v>0.7943600750013654</v>
+        <v>0.8011939957821947</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.37703847194554</v>
+        <v>15.92895193261674</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07526915601528475</v>
+        <v>0.07509730282024188</v>
       </c>
       <c r="C14">
-        <v>103.3209538473593</v>
+        <v>102.668444431426</v>
       </c>
       <c r="D14">
-        <v>117.3729538473593</v>
+        <v>118.061444431426</v>
       </c>
       <c r="E14">
-        <v>-36.908</v>
+        <v>-35.567</v>
       </c>
       <c r="F14">
-        <v>16.092</v>
+        <v>17.433</v>
       </c>
       <c r="G14">
         <v>2.04</v>
@@ -2435,28 +2435,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M14">
-        <v>0.8094275999999999</v>
+        <v>0.8768798999999999</v>
       </c>
       <c r="N14">
-        <v>12.08390573333333</v>
+        <v>12.01645343333333</v>
       </c>
       <c r="O14">
-        <v>3.202235019333333</v>
+        <v>3.184360159833333</v>
       </c>
       <c r="P14">
-        <v>8.881670713999998</v>
+        <v>8.832093273499998</v>
       </c>
       <c r="Q14">
-        <v>13.321670714</v>
+        <v>13.2720932735</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08049170001736902</v>
+        <v>0.08079441128763434</v>
       </c>
       <c r="T14">
-        <v>0.8011939957821947</v>
+        <v>0.8081850181901696</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.92895193261674</v>
+        <v>14.70364793780007</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07509730282024188</v>
+        <v>0.07492544962519901</v>
       </c>
       <c r="C15">
-        <v>102.668444431426</v>
+        <v>102.0240598209911</v>
       </c>
       <c r="D15">
-        <v>118.061444431426</v>
+        <v>118.7580598209911</v>
       </c>
       <c r="E15">
-        <v>-35.567</v>
+        <v>-34.226</v>
       </c>
       <c r="F15">
-        <v>17.433</v>
+        <v>18.774</v>
       </c>
       <c r="G15">
         <v>2.04</v>
@@ -2517,28 +2517,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M15">
-        <v>0.8768798999999999</v>
+        <v>0.9443322</v>
       </c>
       <c r="N15">
-        <v>12.01645343333333</v>
+        <v>11.94900113333333</v>
       </c>
       <c r="O15">
-        <v>3.184360159833333</v>
+        <v>3.166485300333333</v>
       </c>
       <c r="P15">
-        <v>8.832093273499998</v>
+        <v>8.782515832999998</v>
       </c>
       <c r="Q15">
-        <v>13.2720932735</v>
+        <v>13.222515833</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08079441128763434</v>
+        <v>0.08110416235488258</v>
       </c>
       <c r="T15">
-        <v>0.8081850181901696</v>
+        <v>0.8153386225146092</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.70364793780007</v>
+        <v>13.65338737081435</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07492544962519901</v>
+        <v>0.07491897143015615</v>
       </c>
       <c r="C16">
-        <v>102.0240598209911</v>
+        <v>100.7094803240737</v>
       </c>
       <c r="D16">
-        <v>118.7580598209911</v>
+        <v>118.7844803240737</v>
       </c>
       <c r="E16">
-        <v>-34.226</v>
+        <v>-32.885</v>
       </c>
       <c r="F16">
-        <v>18.774</v>
+        <v>20.115</v>
       </c>
       <c r="G16">
         <v>2.04</v>
@@ -2599,45 +2599,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M16">
-        <v>0.9443322</v>
+        <v>1.041957</v>
       </c>
       <c r="N16">
-        <v>11.94900113333333</v>
+        <v>11.85137633333333</v>
       </c>
       <c r="O16">
-        <v>3.166485300333333</v>
+        <v>3.140614728333333</v>
       </c>
       <c r="P16">
-        <v>8.782515832999998</v>
+        <v>8.710761604999998</v>
       </c>
       <c r="Q16">
-        <v>13.222515833</v>
+        <v>13.150761605</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08110416235488258</v>
+        <v>0.08142120168253664</v>
       </c>
       <c r="T16">
-        <v>0.8153386225146092</v>
+        <v>0.8226605469408</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.265</v>
       </c>
       <c r="W16">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.65338737081435</v>
+        <v>12.37415107661192</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07491897143015613</v>
+        <v>0.07475814323511328</v>
       </c>
       <c r="C17">
-        <v>100.7094803240738</v>
+        <v>100.0281874542761</v>
       </c>
       <c r="D17">
-        <v>118.7844803240737</v>
+        <v>119.4441874542761</v>
       </c>
       <c r="E17">
-        <v>-32.88500000000001</v>
+        <v>-31.544</v>
       </c>
       <c r="F17">
-        <v>20.115</v>
+        <v>21.456</v>
       </c>
       <c r="G17">
         <v>2.04</v>
@@ -2681,28 +2681,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M17">
-        <v>1.041957</v>
+        <v>1.1114208</v>
       </c>
       <c r="N17">
-        <v>11.85137633333333</v>
+        <v>11.78191253333333</v>
       </c>
       <c r="O17">
-        <v>3.140614728333333</v>
+        <v>3.122206821333333</v>
       </c>
       <c r="P17">
-        <v>8.710761604999998</v>
+        <v>8.659705711999997</v>
       </c>
       <c r="Q17">
-        <v>13.150761605</v>
+        <v>13.099705712</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08142120168253664</v>
+        <v>0.08174578956561104</v>
       </c>
       <c r="T17">
-        <v>0.8226605469408</v>
+        <v>0.8301568029009481</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.37415107661193</v>
+        <v>11.60076663432368</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07475814323511328</v>
+        <v>0.0745973150400704</v>
       </c>
       <c r="C18">
-        <v>100.0281874542761</v>
+        <v>99.3542632927667</v>
       </c>
       <c r="D18">
-        <v>119.4441874542761</v>
+        <v>120.1112632927667</v>
       </c>
       <c r="E18">
-        <v>-31.544</v>
+        <v>-30.203</v>
       </c>
       <c r="F18">
-        <v>21.456</v>
+        <v>22.797</v>
       </c>
       <c r="G18">
         <v>2.04</v>
@@ -2763,28 +2763,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M18">
-        <v>1.1114208</v>
+        <v>1.1808846</v>
       </c>
       <c r="N18">
-        <v>11.78191253333333</v>
+        <v>11.71244873333333</v>
       </c>
       <c r="O18">
-        <v>3.122206821333333</v>
+        <v>3.103798914333333</v>
       </c>
       <c r="P18">
-        <v>8.659705711999997</v>
+        <v>8.608649818999996</v>
       </c>
       <c r="Q18">
-        <v>13.099705712</v>
+        <v>13.048649819</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08174578956561104</v>
+        <v>0.08207819884345832</v>
       </c>
       <c r="T18">
-        <v>0.8301568029009481</v>
+        <v>0.8378336915348343</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.60076663432368</v>
+        <v>10.91836859701052</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0745973150400704</v>
+        <v>0.07443648684502754</v>
       </c>
       <c r="C19">
-        <v>99.3542632927667</v>
+        <v>98.68783199193125</v>
       </c>
       <c r="D19">
-        <v>120.1112632927667</v>
+        <v>120.7858319919312</v>
       </c>
       <c r="E19">
-        <v>-30.203</v>
+        <v>-28.862</v>
       </c>
       <c r="F19">
-        <v>22.797</v>
+        <v>24.138</v>
       </c>
       <c r="G19">
         <v>2.04</v>
@@ -2845,28 +2845,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M19">
-        <v>1.1808846</v>
+        <v>1.2503484</v>
       </c>
       <c r="N19">
-        <v>11.71244873333333</v>
+        <v>11.64298493333333</v>
       </c>
       <c r="O19">
-        <v>3.103798914333333</v>
+        <v>3.085391007333333</v>
       </c>
       <c r="P19">
-        <v>8.608649818999996</v>
+        <v>8.557593925999997</v>
       </c>
       <c r="Q19">
-        <v>13.048649819</v>
+        <v>12.997593926</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08207819884345832</v>
+        <v>0.08241871566466774</v>
       </c>
       <c r="T19">
-        <v>0.8378336915348343</v>
+        <v>0.8456978213549131</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.91836859701052</v>
+        <v>10.31179256384327</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07443648684502754</v>
+        <v>0.07451306364998467</v>
       </c>
       <c r="C20">
-        <v>98.68783199193126</v>
+        <v>97.02470011458159</v>
       </c>
       <c r="D20">
-        <v>120.7858319919312</v>
+        <v>120.4637001145816</v>
       </c>
       <c r="E20">
-        <v>-28.862</v>
+        <v>-27.521</v>
       </c>
       <c r="F20">
-        <v>24.138</v>
+        <v>25.479</v>
       </c>
       <c r="G20">
         <v>2.04</v>
@@ -2927,45 +2927,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M20">
-        <v>1.2503484</v>
+        <v>1.3631265</v>
       </c>
       <c r="N20">
-        <v>11.64298493333333</v>
+        <v>11.53020683333333</v>
       </c>
       <c r="O20">
-        <v>3.085391007333333</v>
+        <v>3.055504810833333</v>
       </c>
       <c r="P20">
-        <v>8.557593925999997</v>
+        <v>8.474702022499997</v>
       </c>
       <c r="Q20">
-        <v>12.997593926</v>
+        <v>12.9147020225</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08241871566466774</v>
+        <v>0.08276764030862305</v>
       </c>
       <c r="T20">
-        <v>0.8456978213549131</v>
+        <v>0.853756127219932</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.265</v>
       </c>
       <c r="W20">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.31179256384327</v>
+        <v>9.458647699485947</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07451306364998467</v>
+        <v>0.0743647304549418</v>
       </c>
       <c r="C21">
-        <v>97.02470011458159</v>
+        <v>96.30925355898984</v>
       </c>
       <c r="D21">
-        <v>120.4637001145816</v>
+        <v>121.0892535589898</v>
       </c>
       <c r="E21">
-        <v>-27.521</v>
+        <v>-26.18</v>
       </c>
       <c r="F21">
-        <v>25.479</v>
+        <v>26.82</v>
       </c>
       <c r="G21">
         <v>2.04</v>
@@ -3009,28 +3009,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M21">
-        <v>1.3631265</v>
+        <v>1.43487</v>
       </c>
       <c r="N21">
-        <v>11.53020683333333</v>
+        <v>11.45846333333333</v>
       </c>
       <c r="O21">
-        <v>3.055504810833333</v>
+        <v>3.036492783333333</v>
       </c>
       <c r="P21">
-        <v>8.474702022499997</v>
+        <v>8.421970549999998</v>
       </c>
       <c r="Q21">
-        <v>12.9147020225</v>
+        <v>12.86197055</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08276764030862305</v>
+        <v>0.08312528806867725</v>
       </c>
       <c r="T21">
-        <v>0.853756127219932</v>
+        <v>0.8620158907315765</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.458647699485947</v>
+        <v>8.98571531451165</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0743647304549418</v>
+        <v>0.07421639725989895</v>
       </c>
       <c r="C22">
-        <v>96.30925355898984</v>
+        <v>95.60033776380583</v>
       </c>
       <c r="D22">
-        <v>121.0892535589898</v>
+        <v>121.7213377638058</v>
       </c>
       <c r="E22">
-        <v>-26.18</v>
+        <v>-24.839</v>
       </c>
       <c r="F22">
-        <v>26.82</v>
+        <v>28.161</v>
       </c>
       <c r="G22">
         <v>2.04</v>
@@ -3091,28 +3091,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M22">
-        <v>1.43487</v>
+        <v>1.5066135</v>
       </c>
       <c r="N22">
-        <v>11.45846333333333</v>
+        <v>11.38671983333333</v>
       </c>
       <c r="O22">
-        <v>3.036492783333333</v>
+        <v>3.017480755833333</v>
       </c>
       <c r="P22">
-        <v>8.421970549999998</v>
+        <v>8.369239077499998</v>
       </c>
       <c r="Q22">
-        <v>12.86197055</v>
+        <v>12.8092390775</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08312528806867725</v>
+        <v>0.08349199020240372</v>
       </c>
       <c r="T22">
-        <v>0.8620158907315765</v>
+        <v>0.8704847621802245</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.98571531451165</v>
+        <v>8.557824109058714</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07421639725989894</v>
+        <v>0.07406806406485607</v>
       </c>
       <c r="C23">
-        <v>95.60033776380588</v>
+        <v>94.89805553711972</v>
       </c>
       <c r="D23">
-        <v>121.7213377638059</v>
+        <v>122.3600555371197</v>
       </c>
       <c r="E23">
-        <v>-24.839</v>
+        <v>-23.498</v>
       </c>
       <c r="F23">
-        <v>28.161</v>
+        <v>29.502</v>
       </c>
       <c r="G23">
         <v>2.04</v>
@@ -3173,28 +3173,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M23">
-        <v>1.5066135</v>
+        <v>1.578357</v>
       </c>
       <c r="N23">
-        <v>11.38671983333333</v>
+        <v>11.31497633333333</v>
       </c>
       <c r="O23">
-        <v>3.017480755833333</v>
+        <v>2.998468728333333</v>
       </c>
       <c r="P23">
-        <v>8.369239077499998</v>
+        <v>8.316507604999998</v>
       </c>
       <c r="Q23">
-        <v>12.8092390775</v>
+        <v>12.756507605</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08349199020240372</v>
+        <v>0.08386809495494367</v>
       </c>
       <c r="T23">
-        <v>0.8704847621802245</v>
+        <v>0.8791707841788379</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.557824109058714</v>
+        <v>8.168832104101499</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07406806406485607</v>
+        <v>0.0739197308698132</v>
       </c>
       <c r="C24">
-        <v>94.89805553711972</v>
+        <v>94.20251185629553</v>
       </c>
       <c r="D24">
-        <v>122.3600555371197</v>
+        <v>123.0055118562955</v>
       </c>
       <c r="E24">
-        <v>-23.498</v>
+        <v>-22.157</v>
       </c>
       <c r="F24">
-        <v>29.502</v>
+        <v>30.843</v>
       </c>
       <c r="G24">
         <v>2.04</v>
@@ -3255,28 +3255,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M24">
-        <v>1.578357</v>
+        <v>1.6501005</v>
       </c>
       <c r="N24">
-        <v>11.31497633333333</v>
+        <v>11.24323283333333</v>
       </c>
       <c r="O24">
-        <v>2.998468728333333</v>
+        <v>2.979456700833333</v>
       </c>
       <c r="P24">
-        <v>8.316507604999998</v>
+        <v>8.263776132499999</v>
       </c>
       <c r="Q24">
-        <v>12.756507605</v>
+        <v>12.7037761325</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08386809495494367</v>
+        <v>0.08425396866209506</v>
       </c>
       <c r="T24">
-        <v>0.8791707841788379</v>
+        <v>0.8880824171384543</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.168832104101499</v>
+        <v>7.813665490879695</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0739197308698132</v>
+        <v>0.07391251767477033</v>
       </c>
       <c r="C25">
-        <v>94.20251185629553</v>
+        <v>92.89307298357099</v>
       </c>
       <c r="D25">
-        <v>123.0055118562955</v>
+        <v>123.037072983571</v>
       </c>
       <c r="E25">
-        <v>-22.157</v>
+        <v>-20.816</v>
       </c>
       <c r="F25">
-        <v>30.843</v>
+        <v>32.184</v>
       </c>
       <c r="G25">
         <v>2.04</v>
@@ -3337,45 +3337,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M25">
-        <v>1.6501005</v>
+        <v>1.7475912</v>
       </c>
       <c r="N25">
-        <v>11.24323283333333</v>
+        <v>11.14574213333333</v>
       </c>
       <c r="O25">
-        <v>2.979456700833333</v>
+        <v>2.953621665333333</v>
       </c>
       <c r="P25">
-        <v>8.263776132499999</v>
+        <v>8.192120467999997</v>
       </c>
       <c r="Q25">
-        <v>12.7037761325</v>
+        <v>12.632120468</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08425396866209506</v>
+        <v>0.08464999694048728</v>
       </c>
       <c r="T25">
-        <v>0.8880824171384543</v>
+        <v>0.8972285667549027</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.265</v>
       </c>
       <c r="W25">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.813665490879695</v>
+        <v>7.377774237666869</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07391251767477033</v>
+        <v>0.07377006447972746</v>
       </c>
       <c r="C26">
-        <v>92.89307298357099</v>
+        <v>92.17870808367724</v>
       </c>
       <c r="D26">
-        <v>123.037072983571</v>
+        <v>123.6637080836772</v>
       </c>
       <c r="E26">
-        <v>-20.816</v>
+        <v>-19.475</v>
       </c>
       <c r="F26">
-        <v>32.184</v>
+        <v>33.525</v>
       </c>
       <c r="G26">
         <v>2.04</v>
@@ -3419,28 +3419,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M26">
-        <v>1.7475912</v>
+        <v>1.8204075</v>
       </c>
       <c r="N26">
-        <v>11.14574213333333</v>
+        <v>11.07292583333333</v>
       </c>
       <c r="O26">
-        <v>2.953621665333333</v>
+        <v>2.934325345833333</v>
       </c>
       <c r="P26">
-        <v>8.192120467999997</v>
+        <v>8.138600487499998</v>
       </c>
       <c r="Q26">
-        <v>12.632120468</v>
+        <v>12.5786004875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08464999694048728</v>
+        <v>0.08505658597296994</v>
       </c>
       <c r="T26">
-        <v>0.8972285667549027</v>
+        <v>0.9066186136944564</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.377774237666871</v>
+        <v>7.082663268160196</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07377006447972746</v>
+        <v>0.0736276112846846</v>
       </c>
       <c r="C27">
-        <v>92.17870808367724</v>
+        <v>91.47075883845268</v>
       </c>
       <c r="D27">
-        <v>123.6637080836772</v>
+        <v>124.2967588384527</v>
       </c>
       <c r="E27">
-        <v>-19.475</v>
+        <v>-18.134</v>
       </c>
       <c r="F27">
-        <v>33.525</v>
+        <v>34.866</v>
       </c>
       <c r="G27">
         <v>2.04</v>
@@ -3501,28 +3501,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M27">
-        <v>1.8204075</v>
+        <v>1.8932238</v>
       </c>
       <c r="N27">
-        <v>11.07292583333333</v>
+        <v>11.00010953333333</v>
       </c>
       <c r="O27">
-        <v>2.934325345833333</v>
+        <v>2.915029026333333</v>
       </c>
       <c r="P27">
-        <v>8.138600487499998</v>
+        <v>8.085080506999999</v>
       </c>
       <c r="Q27">
-        <v>12.5786004875</v>
+        <v>12.525080507</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08505658597296994</v>
+        <v>0.08547416389822243</v>
       </c>
       <c r="T27">
-        <v>0.9066186136944564</v>
+        <v>0.9162624456864304</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.082663268160196</v>
+        <v>6.810253142461726</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0736276112846846</v>
+        <v>0.07348515808964172</v>
       </c>
       <c r="C28">
-        <v>91.47075883845268</v>
+        <v>90.7693242826044</v>
       </c>
       <c r="D28">
-        <v>124.2967588384527</v>
+        <v>124.9363242826044</v>
       </c>
       <c r="E28">
-        <v>-18.134</v>
+        <v>-16.793</v>
       </c>
       <c r="F28">
-        <v>34.866</v>
+        <v>36.207</v>
       </c>
       <c r="G28">
         <v>2.04</v>
@@ -3583,28 +3583,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M28">
-        <v>1.8932238</v>
+        <v>1.9660401</v>
       </c>
       <c r="N28">
-        <v>11.00010953333333</v>
+        <v>10.92729323333333</v>
       </c>
       <c r="O28">
-        <v>2.915029026333333</v>
+        <v>2.895732706833333</v>
       </c>
       <c r="P28">
-        <v>8.085080506999999</v>
+        <v>8.031560526499998</v>
       </c>
       <c r="Q28">
-        <v>12.525080507</v>
+        <v>12.4715605265</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08547416389822243</v>
+        <v>0.08590318231457771</v>
       </c>
       <c r="T28">
-        <v>0.9162624456864304</v>
+        <v>0.9261704922535269</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.810253142461726</v>
+        <v>6.558021544592773</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07348515808964172</v>
+        <v>0.07334270489459885</v>
       </c>
       <c r="C29">
-        <v>90.7693242826044</v>
+        <v>90.07450549970264</v>
       </c>
       <c r="D29">
-        <v>124.9363242826044</v>
+        <v>125.5825054997026</v>
       </c>
       <c r="E29">
-        <v>-16.793</v>
+        <v>-15.452</v>
       </c>
       <c r="F29">
-        <v>36.207</v>
+        <v>37.548</v>
       </c>
       <c r="G29">
         <v>2.04</v>
@@ -3665,28 +3665,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M29">
-        <v>1.9660401</v>
+        <v>2.0388564</v>
       </c>
       <c r="N29">
-        <v>10.92729323333333</v>
+        <v>10.85447693333333</v>
       </c>
       <c r="O29">
-        <v>2.895732706833333</v>
+        <v>2.876436387333333</v>
       </c>
       <c r="P29">
-        <v>8.031560526499998</v>
+        <v>7.978040545999997</v>
       </c>
       <c r="Q29">
-        <v>12.4715605265</v>
+        <v>12.418040546</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08590318231457771</v>
+        <v>0.08634411790916507</v>
       </c>
       <c r="T29">
-        <v>0.9261704922535269</v>
+        <v>0.9363537623363762</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.558021544592773</v>
+        <v>6.323806489428745</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07334270489459885</v>
+        <v>0.073413401699556</v>
       </c>
       <c r="C30">
-        <v>90.07450549970264</v>
+        <v>88.41198473982155</v>
       </c>
       <c r="D30">
-        <v>125.5825054997026</v>
+        <v>125.2609847398216</v>
       </c>
       <c r="E30">
-        <v>-15.452</v>
+        <v>-14.111</v>
       </c>
       <c r="F30">
-        <v>37.548</v>
+        <v>38.889</v>
       </c>
       <c r="G30">
         <v>2.04</v>
@@ -3747,45 +3747,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M30">
-        <v>2.0388564</v>
+        <v>2.1505617</v>
       </c>
       <c r="N30">
-        <v>10.85447693333333</v>
+        <v>10.74277163333333</v>
       </c>
       <c r="O30">
-        <v>2.876436387333333</v>
+        <v>2.846834482833333</v>
       </c>
       <c r="P30">
-        <v>7.978040545999997</v>
+        <v>7.895937150499997</v>
       </c>
       <c r="Q30">
-        <v>12.418040546</v>
+        <v>12.3359371505</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08634411790916507</v>
+        <v>0.08679747422472675</v>
       </c>
       <c r="T30">
-        <v>0.9363537623363762</v>
+        <v>0.9468238850976157</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.265</v>
       </c>
       <c r="W30">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.323806489428745</v>
+        <v>5.995332909227077</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07341340169955599</v>
+        <v>0.07327829850451312</v>
       </c>
       <c r="C31">
-        <v>88.41198473982162</v>
+        <v>87.6868583627749</v>
       </c>
       <c r="D31">
-        <v>125.2609847398216</v>
+        <v>125.8768583627749</v>
       </c>
       <c r="E31">
-        <v>-14.111</v>
+        <v>-12.77</v>
       </c>
       <c r="F31">
-        <v>38.889</v>
+        <v>40.23</v>
       </c>
       <c r="G31">
         <v>2.04</v>
@@ -3829,28 +3829,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M31">
-        <v>2.1505617</v>
+        <v>2.224719</v>
       </c>
       <c r="N31">
-        <v>10.74277163333333</v>
+        <v>10.66861433333333</v>
       </c>
       <c r="O31">
-        <v>2.846834482833333</v>
+        <v>2.827182798333333</v>
       </c>
       <c r="P31">
-        <v>7.895937150499997</v>
+        <v>7.841431534999998</v>
       </c>
       <c r="Q31">
-        <v>12.3359371505</v>
+        <v>12.281431535</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08679747422472675</v>
+        <v>0.0872637835778759</v>
       </c>
       <c r="T31">
-        <v>0.9468238850976157</v>
+        <v>0.9575931542234618</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.995332909227078</v>
+        <v>5.795488478919509</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07327829850451312</v>
+        <v>0.07314319530947025</v>
       </c>
       <c r="C32">
-        <v>87.6868583627749</v>
+        <v>86.96781806990828</v>
       </c>
       <c r="D32">
-        <v>125.8768583627749</v>
+        <v>126.4988180699083</v>
       </c>
       <c r="E32">
-        <v>-12.77</v>
+        <v>-11.429</v>
       </c>
       <c r="F32">
-        <v>40.23</v>
+        <v>41.571</v>
       </c>
       <c r="G32">
         <v>2.04</v>
@@ -3911,28 +3911,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M32">
-        <v>2.224719</v>
+        <v>2.2988763</v>
       </c>
       <c r="N32">
-        <v>10.66861433333333</v>
+        <v>10.59445703333333</v>
       </c>
       <c r="O32">
-        <v>2.827182798333333</v>
+        <v>2.807531113833333</v>
       </c>
       <c r="P32">
-        <v>7.841431534999998</v>
+        <v>7.786925919499998</v>
       </c>
       <c r="Q32">
-        <v>12.281431535</v>
+        <v>12.2269259195</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0872637835778759</v>
+        <v>0.0877436091441598</v>
       </c>
       <c r="T32">
-        <v>0.9575931542234618</v>
+        <v>0.9686745760775936</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.795488478919509</v>
+        <v>5.608537237664041</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07314319530947025</v>
+        <v>0.07300809211442738</v>
       </c>
       <c r="C33">
-        <v>86.96781806990828</v>
+        <v>86.25495452352342</v>
       </c>
       <c r="D33">
-        <v>126.4988180699083</v>
+        <v>127.1269545235234</v>
       </c>
       <c r="E33">
-        <v>-11.429</v>
+        <v>-10.088</v>
       </c>
       <c r="F33">
-        <v>41.571</v>
+        <v>42.912</v>
       </c>
       <c r="G33">
         <v>2.04</v>
@@ -3993,28 +3993,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M33">
-        <v>2.2988763</v>
+        <v>2.3730336</v>
       </c>
       <c r="N33">
-        <v>10.59445703333333</v>
+        <v>10.52029973333333</v>
       </c>
       <c r="O33">
-        <v>2.807531113833333</v>
+        <v>2.787879429333333</v>
       </c>
       <c r="P33">
-        <v>7.786925919499998</v>
+        <v>7.732420303999998</v>
       </c>
       <c r="Q33">
-        <v>12.2269259195</v>
+        <v>12.172420304</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0877436091441598</v>
+        <v>0.0882375472270991</v>
       </c>
       <c r="T33">
-        <v>0.9686745760775936</v>
+        <v>0.9800819221039055</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.608537237664041</v>
+        <v>5.43327044898704</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07300809211442738</v>
+        <v>0.07287298891938451</v>
       </c>
       <c r="C34">
-        <v>86.25495452352342</v>
+        <v>85.54836019566183</v>
       </c>
       <c r="D34">
-        <v>127.1269545235234</v>
+        <v>127.7613601956618</v>
       </c>
       <c r="E34">
-        <v>-10.088</v>
+        <v>-8.747</v>
       </c>
       <c r="F34">
-        <v>42.912</v>
+        <v>44.253</v>
       </c>
       <c r="G34">
         <v>2.04</v>
@@ -4075,28 +4075,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M34">
-        <v>2.3730336</v>
+        <v>2.4471909</v>
       </c>
       <c r="N34">
-        <v>10.52029973333333</v>
+        <v>10.44614243333333</v>
       </c>
       <c r="O34">
-        <v>2.787879429333333</v>
+        <v>2.768227744833333</v>
       </c>
       <c r="P34">
-        <v>7.732420303999998</v>
+        <v>7.677914688499998</v>
       </c>
       <c r="Q34">
-        <v>12.172420304</v>
+        <v>12.1179146885</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0882375472270991</v>
+        <v>0.08874622973042466</v>
       </c>
       <c r="T34">
-        <v>0.9800819221039055</v>
+        <v>0.9918297859220477</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.43327044898704</v>
+        <v>5.268625889926826</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07287298891938451</v>
+        <v>0.07273788572434166</v>
       </c>
       <c r="C35">
-        <v>85.54836019566183</v>
+        <v>84.84812941348719</v>
       </c>
       <c r="D35">
-        <v>127.7613601956618</v>
+        <v>128.4021294134872</v>
       </c>
       <c r="E35">
-        <v>-8.747</v>
+        <v>-7.405999999999999</v>
       </c>
       <c r="F35">
-        <v>44.253</v>
+        <v>45.594</v>
       </c>
       <c r="G35">
         <v>2.04</v>
@@ -4157,28 +4157,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M35">
-        <v>2.4471909</v>
+        <v>2.5213482</v>
       </c>
       <c r="N35">
-        <v>10.44614243333333</v>
+        <v>10.37198513333333</v>
       </c>
       <c r="O35">
-        <v>2.768227744833333</v>
+        <v>2.748576060333333</v>
       </c>
       <c r="P35">
-        <v>7.677914688499998</v>
+        <v>7.623409072999998</v>
       </c>
       <c r="Q35">
-        <v>12.1179146885</v>
+        <v>12.063409073</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08874622973042466</v>
+        <v>0.08927032685506311</v>
       </c>
       <c r="T35">
-        <v>0.9918297859220477</v>
+        <v>1.003933645613467</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.268625889926826</v>
+        <v>5.113666304928978</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07273788572434166</v>
+        <v>0.07260278252929879</v>
       </c>
       <c r="C36">
-        <v>84.84812941348719</v>
+        <v>84.15435840604073</v>
       </c>
       <c r="D36">
-        <v>128.4021294134872</v>
+        <v>129.0493584060407</v>
       </c>
       <c r="E36">
-        <v>-7.405999999999999</v>
+        <v>-6.064999999999998</v>
       </c>
       <c r="F36">
-        <v>45.594</v>
+        <v>46.935</v>
       </c>
       <c r="G36">
         <v>2.04</v>
@@ -4239,28 +4239,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M36">
-        <v>2.5213482</v>
+        <v>2.5955055</v>
       </c>
       <c r="N36">
-        <v>10.37198513333333</v>
+        <v>10.29782783333333</v>
       </c>
       <c r="O36">
-        <v>2.748576060333333</v>
+        <v>2.728924375833333</v>
       </c>
       <c r="P36">
-        <v>7.623409072999998</v>
+        <v>7.568903457499998</v>
       </c>
       <c r="Q36">
-        <v>12.063409073</v>
+        <v>12.0089034575</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08927032685506311</v>
+        <v>0.08981055004507506</v>
       </c>
       <c r="T36">
-        <v>1.003933645613467</v>
+        <v>1.01640993175693</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.113666304928978</v>
+        <v>4.967561553359578</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07260278252929879</v>
+        <v>0.07246767933425592</v>
       </c>
       <c r="C37">
-        <v>84.15435840604073</v>
+        <v>83.46714535241713</v>
       </c>
       <c r="D37">
-        <v>129.0493584060407</v>
+        <v>129.7031453524172</v>
       </c>
       <c r="E37">
-        <v>-6.064999999999998</v>
+        <v>-4.723999999999997</v>
       </c>
       <c r="F37">
-        <v>46.935</v>
+        <v>48.276</v>
       </c>
       <c r="G37">
         <v>2.04</v>
@@ -4321,28 +4321,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M37">
-        <v>2.5955055</v>
+        <v>2.6696628</v>
       </c>
       <c r="N37">
-        <v>10.29782783333333</v>
+        <v>10.22367053333333</v>
       </c>
       <c r="O37">
-        <v>2.728924375833333</v>
+        <v>2.709272691333333</v>
       </c>
       <c r="P37">
-        <v>7.568903457499998</v>
+        <v>7.514397841999997</v>
       </c>
       <c r="Q37">
-        <v>12.0089034575</v>
+        <v>11.954397842</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08981055004507506</v>
+        <v>0.09036765520977488</v>
       </c>
       <c r="T37">
-        <v>1.01640993175693</v>
+        <v>1.029276101842376</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.967561553359578</v>
+        <v>4.829573732432923</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07246767933425594</v>
+        <v>0.07233257613921304</v>
       </c>
       <c r="C38">
-        <v>83.46714535241706</v>
+        <v>82.78659043141286</v>
       </c>
       <c r="D38">
-        <v>129.7031453524171</v>
+        <v>130.3635904314129</v>
       </c>
       <c r="E38">
-        <v>-4.724000000000004</v>
+        <v>-3.383000000000003</v>
       </c>
       <c r="F38">
-        <v>48.276</v>
+        <v>49.617</v>
       </c>
       <c r="G38">
         <v>2.04</v>
@@ -4403,28 +4403,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M38">
-        <v>2.6696628</v>
+        <v>2.7438201</v>
       </c>
       <c r="N38">
-        <v>10.22367053333333</v>
+        <v>10.14951323333333</v>
       </c>
       <c r="O38">
-        <v>2.709272691333333</v>
+        <v>2.689621006833333</v>
       </c>
       <c r="P38">
-        <v>7.514397841999998</v>
+        <v>7.459892226499997</v>
       </c>
       <c r="Q38">
-        <v>11.954397842</v>
+        <v>11.8998922265</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09036765520977488</v>
+        <v>0.09094244625271912</v>
       </c>
       <c r="T38">
-        <v>1.029276101842376</v>
+        <v>1.042550721771804</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.829573732432925</v>
+        <v>4.69904471263744</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07233257613921304</v>
+        <v>0.07219747294417017</v>
       </c>
       <c r="C39">
-        <v>82.78659043141286</v>
+        <v>82.11279587269863</v>
       </c>
       <c r="D39">
-        <v>130.3635904314129</v>
+        <v>131.0307958726986</v>
       </c>
       <c r="E39">
-        <v>-3.383000000000003</v>
+        <v>-2.042000000000002</v>
       </c>
       <c r="F39">
-        <v>49.617</v>
+        <v>50.958</v>
       </c>
       <c r="G39">
         <v>2.04</v>
@@ -4485,28 +4485,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M39">
-        <v>2.7438201</v>
+        <v>2.8179774</v>
       </c>
       <c r="N39">
-        <v>10.14951323333333</v>
+        <v>10.07535593333333</v>
       </c>
       <c r="O39">
-        <v>2.689621006833333</v>
+        <v>2.669969322333333</v>
       </c>
       <c r="P39">
-        <v>7.459892226499997</v>
+        <v>7.405386610999997</v>
       </c>
       <c r="Q39">
-        <v>11.8998922265</v>
+        <v>11.845386611</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09094244625271912</v>
+        <v>0.09153577894220996</v>
       </c>
       <c r="T39">
-        <v>1.042550721771804</v>
+        <v>1.056253555247344</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.69904471263744</v>
+        <v>4.575385641252243</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07219747294417017</v>
+        <v>0.0727789947491273</v>
       </c>
       <c r="C40">
-        <v>82.11279587269863</v>
+        <v>77.94747770853402</v>
       </c>
       <c r="D40">
-        <v>131.0307958726986</v>
+        <v>128.206477708534</v>
       </c>
       <c r="E40">
-        <v>-2.042000000000002</v>
+        <v>-0.7010000000000005</v>
       </c>
       <c r="F40">
-        <v>50.958</v>
+        <v>52.299</v>
       </c>
       <c r="G40">
         <v>2.04</v>
@@ -4567,45 +4567,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M40">
-        <v>2.8179774</v>
+        <v>3.0228822</v>
       </c>
       <c r="N40">
-        <v>10.07535593333333</v>
+        <v>9.870451133333331</v>
       </c>
       <c r="O40">
-        <v>2.669969322333333</v>
+        <v>2.615669550333333</v>
       </c>
       <c r="P40">
-        <v>7.405386610999997</v>
+        <v>7.254781582999998</v>
       </c>
       <c r="Q40">
-        <v>11.845386611</v>
+        <v>11.694781583</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09153577894220996</v>
+        <v>0.09214856516250379</v>
       </c>
       <c r="T40">
-        <v>1.056253555247344</v>
+        <v>1.070405661951589</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.265</v>
       </c>
       <c r="W40">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.575385641252243</v>
+        <v>4.265245047700942</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0727789947491273</v>
+        <v>0.07266226655408445</v>
       </c>
       <c r="C41">
-        <v>77.94747770853402</v>
+        <v>77.16359044157865</v>
       </c>
       <c r="D41">
-        <v>128.206477708534</v>
+        <v>128.7635904415787</v>
       </c>
       <c r="E41">
-        <v>-0.7010000000000005</v>
+        <v>0.6400000000000006</v>
       </c>
       <c r="F41">
-        <v>52.299</v>
+        <v>53.64</v>
       </c>
       <c r="G41">
         <v>2.04</v>
@@ -4649,28 +4649,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M41">
-        <v>3.0228822</v>
+        <v>3.100392</v>
       </c>
       <c r="N41">
-        <v>9.870451133333331</v>
+        <v>9.792941333333331</v>
       </c>
       <c r="O41">
-        <v>2.615669550333333</v>
+        <v>2.595129453333333</v>
       </c>
       <c r="P41">
-        <v>7.254781582999998</v>
+        <v>7.197811879999998</v>
       </c>
       <c r="Q41">
-        <v>11.694781583</v>
+        <v>11.63781188</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09214856516250379</v>
+        <v>0.09278177759014075</v>
       </c>
       <c r="T41">
-        <v>1.070405661951589</v>
+        <v>1.085029505545976</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.265245047700942</v>
+        <v>4.158613921508419</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07266226655408445</v>
+        <v>0.07254553835904157</v>
       </c>
       <c r="C42">
-        <v>77.16359044157865</v>
+        <v>76.38456609889067</v>
       </c>
       <c r="D42">
-        <v>128.7635904415787</v>
+        <v>129.3255660988907</v>
       </c>
       <c r="E42">
-        <v>0.6400000000000006</v>
+        <v>1.981000000000002</v>
       </c>
       <c r="F42">
-        <v>53.64</v>
+        <v>54.981</v>
       </c>
       <c r="G42">
         <v>2.04</v>
@@ -4731,28 +4731,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M42">
-        <v>3.100392</v>
+        <v>3.1779018</v>
       </c>
       <c r="N42">
-        <v>9.792941333333331</v>
+        <v>9.71543153333333</v>
       </c>
       <c r="O42">
-        <v>2.595129453333333</v>
+        <v>2.574589356333333</v>
       </c>
       <c r="P42">
-        <v>7.197811879999998</v>
+        <v>7.140842176999998</v>
       </c>
       <c r="Q42">
-        <v>11.63781188</v>
+        <v>11.580842177</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09278177759014075</v>
+        <v>0.09343645484583318</v>
       </c>
       <c r="T42">
-        <v>1.085029505545976</v>
+        <v>1.100149072652037</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.158613921508419</v>
+        <v>4.05718431366675</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07254553835904157</v>
+        <v>0.07350926016399871</v>
       </c>
       <c r="C43">
-        <v>76.38456609889067</v>
+        <v>70.54565214340161</v>
       </c>
       <c r="D43">
-        <v>129.3255660988907</v>
+        <v>124.8276521434016</v>
       </c>
       <c r="E43">
-        <v>1.981000000000002</v>
+        <v>3.322000000000003</v>
       </c>
       <c r="F43">
-        <v>54.981</v>
+        <v>56.322</v>
       </c>
       <c r="G43">
         <v>2.04</v>
@@ -4813,45 +4813,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M43">
-        <v>3.1779018</v>
+        <v>3.4525386</v>
       </c>
       <c r="N43">
-        <v>9.71543153333333</v>
+        <v>9.44079473333333</v>
       </c>
       <c r="O43">
-        <v>2.574589356333333</v>
+        <v>2.501810604333333</v>
       </c>
       <c r="P43">
-        <v>7.140842176999998</v>
+        <v>6.938984128999998</v>
       </c>
       <c r="Q43">
-        <v>11.580842177</v>
+        <v>11.378984129</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09343645484583318</v>
+        <v>0.09411370717930813</v>
       </c>
       <c r="T43">
-        <v>1.100149072652037</v>
+        <v>1.115790004141066</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.265</v>
       </c>
       <c r="W43">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.05718431366675</v>
+        <v>3.73445016178337</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07350926016399872</v>
+        <v>0.07341825696895586</v>
       </c>
       <c r="C44">
-        <v>70.54565214340155</v>
+        <v>69.61596395020811</v>
       </c>
       <c r="D44">
-        <v>124.8276521434016</v>
+        <v>125.2389639502081</v>
       </c>
       <c r="E44">
-        <v>3.321999999999996</v>
+        <v>4.662999999999997</v>
       </c>
       <c r="F44">
-        <v>56.322</v>
+        <v>57.663</v>
       </c>
       <c r="G44">
         <v>2.04</v>
@@ -4895,28 +4895,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M44">
-        <v>3.4525386</v>
+        <v>3.5347419</v>
       </c>
       <c r="N44">
-        <v>9.44079473333333</v>
+        <v>9.358591433333331</v>
       </c>
       <c r="O44">
-        <v>2.501810604333333</v>
+        <v>2.480026729833333</v>
       </c>
       <c r="P44">
-        <v>6.938984128999998</v>
+        <v>6.878564703499998</v>
       </c>
       <c r="Q44">
-        <v>11.378984129</v>
+        <v>11.3185647035</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09411370717930813</v>
+        <v>0.09481472275255412</v>
       </c>
       <c r="T44">
-        <v>1.115790004141066</v>
+        <v>1.131979740243744</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.734450161783371</v>
+        <v>3.647602483602362</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07341825696895586</v>
+        <v>0.07332725377391297</v>
       </c>
       <c r="C45">
-        <v>69.61596395020811</v>
+        <v>68.6889952937245</v>
       </c>
       <c r="D45">
-        <v>125.2389639502081</v>
+        <v>125.6529952937245</v>
       </c>
       <c r="E45">
-        <v>4.662999999999997</v>
+        <v>6.003999999999998</v>
       </c>
       <c r="F45">
-        <v>57.663</v>
+        <v>59.004</v>
       </c>
       <c r="G45">
         <v>2.04</v>
@@ -4977,28 +4977,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M45">
-        <v>3.5347419</v>
+        <v>3.6169452</v>
       </c>
       <c r="N45">
-        <v>9.358591433333331</v>
+        <v>9.276388133333331</v>
       </c>
       <c r="O45">
-        <v>2.480026729833333</v>
+        <v>2.458242855333333</v>
       </c>
       <c r="P45">
-        <v>6.878564703499998</v>
+        <v>6.818145277999998</v>
       </c>
       <c r="Q45">
-        <v>11.3185647035</v>
+        <v>11.258145278</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09481472275255412</v>
+        <v>0.09554077459627316</v>
       </c>
       <c r="T45">
-        <v>1.131979740243744</v>
+        <v>1.148747681207233</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.647602483602362</v>
+        <v>3.564702427156853</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07332725377391297</v>
+        <v>0.07416235057887012</v>
       </c>
       <c r="C46">
-        <v>68.6889952937245</v>
+        <v>63.64828730896885</v>
       </c>
       <c r="D46">
-        <v>125.6529952937245</v>
+        <v>121.9532873089688</v>
       </c>
       <c r="E46">
-        <v>6.003999999999998</v>
+        <v>7.344999999999999</v>
       </c>
       <c r="F46">
-        <v>59.004</v>
+        <v>60.345</v>
       </c>
       <c r="G46">
         <v>2.04</v>
@@ -5059,45 +5059,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M46">
-        <v>3.6169452</v>
+        <v>3.8681145</v>
       </c>
       <c r="N46">
-        <v>9.276388133333331</v>
+        <v>9.02521883333333</v>
       </c>
       <c r="O46">
-        <v>2.458242855333333</v>
+        <v>2.391682990833333</v>
       </c>
       <c r="P46">
-        <v>6.818145277999998</v>
+        <v>6.633535842499997</v>
       </c>
       <c r="Q46">
-        <v>11.258145278</v>
+        <v>11.0735358425</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09554077459627316</v>
+        <v>0.09629322832521837</v>
       </c>
       <c r="T46">
-        <v>1.148747681207233</v>
+        <v>1.166125365478485</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.265</v>
       </c>
       <c r="W46">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.564702427156853</v>
+        <v>3.333234663382723</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07416235057887012</v>
+        <v>0.07409192738382725</v>
       </c>
       <c r="C47">
-        <v>63.64828730896885</v>
+        <v>62.61084881687757</v>
       </c>
       <c r="D47">
-        <v>121.9532873089688</v>
+        <v>122.2568488168776</v>
       </c>
       <c r="E47">
-        <v>7.344999999999999</v>
+        <v>8.686</v>
       </c>
       <c r="F47">
-        <v>60.345</v>
+        <v>61.686</v>
       </c>
       <c r="G47">
         <v>2.04</v>
@@ -5141,28 +5141,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M47">
-        <v>3.8681145</v>
+        <v>3.9540726</v>
       </c>
       <c r="N47">
-        <v>9.02521883333333</v>
+        <v>8.939260733333331</v>
       </c>
       <c r="O47">
-        <v>2.391682990833333</v>
+        <v>2.368904094333333</v>
       </c>
       <c r="P47">
-        <v>6.633535842499997</v>
+        <v>6.570356638999998</v>
       </c>
       <c r="Q47">
-        <v>11.0735358425</v>
+        <v>11.010356639</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09629322832521837</v>
+        <v>0.09707355071079118</v>
       </c>
       <c r="T47">
-        <v>1.166125365478485</v>
+        <v>1.184146667685709</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.333234663382723</v>
+        <v>3.260773040265707</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07409192738382725</v>
+        <v>0.07402150418878438</v>
       </c>
       <c r="C48">
-        <v>62.61084881687757</v>
+        <v>61.57492532350047</v>
       </c>
       <c r="D48">
-        <v>122.2568488168776</v>
+        <v>122.5619253235005</v>
       </c>
       <c r="E48">
-        <v>8.686</v>
+        <v>10.027</v>
       </c>
       <c r="F48">
-        <v>61.686</v>
+        <v>63.027</v>
       </c>
       <c r="G48">
         <v>2.04</v>
@@ -5223,28 +5223,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M48">
-        <v>3.9540726</v>
+        <v>4.0400307</v>
       </c>
       <c r="N48">
-        <v>8.939260733333331</v>
+        <v>8.853302633333332</v>
       </c>
       <c r="O48">
-        <v>2.368904094333333</v>
+        <v>2.346125197833333</v>
       </c>
       <c r="P48">
-        <v>6.570356638999998</v>
+        <v>6.507177435499999</v>
       </c>
       <c r="Q48">
-        <v>11.010356639</v>
+        <v>10.9471774355</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09707355071079118</v>
+        <v>0.09788331922412147</v>
       </c>
       <c r="T48">
-        <v>1.184146667685709</v>
+        <v>1.202848019032829</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.260773040265707</v>
+        <v>3.19139489047282</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07402150418878438</v>
+        <v>0.07395108099374151</v>
       </c>
       <c r="C49">
-        <v>61.57492532350047</v>
+        <v>60.54052819867266</v>
       </c>
       <c r="D49">
-        <v>122.5619253235005</v>
+        <v>122.8685281986727</v>
       </c>
       <c r="E49">
-        <v>10.027</v>
+        <v>11.36800000000001</v>
       </c>
       <c r="F49">
-        <v>63.027</v>
+        <v>64.36800000000001</v>
       </c>
       <c r="G49">
         <v>2.04</v>
@@ -5305,28 +5305,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M49">
-        <v>4.0400307</v>
+        <v>4.125988800000001</v>
       </c>
       <c r="N49">
-        <v>8.853302633333332</v>
+        <v>8.767344533333329</v>
       </c>
       <c r="O49">
-        <v>2.346125197833333</v>
+        <v>2.323346301333332</v>
       </c>
       <c r="P49">
-        <v>6.507177435499999</v>
+        <v>6.443998231999997</v>
       </c>
       <c r="Q49">
-        <v>10.9471774355</v>
+        <v>10.883998232</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09788331922412147</v>
+        <v>0.09872423268027213</v>
       </c>
       <c r="T49">
-        <v>1.202848019032829</v>
+        <v>1.222268653124068</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.19139489047282</v>
+        <v>3.124907496921302</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07395108099374151</v>
+        <v>0.07388065779869864</v>
       </c>
       <c r="C50">
-        <v>60.54052819867267</v>
+        <v>59.50766892628648</v>
       </c>
       <c r="D50">
-        <v>122.8685281986727</v>
+        <v>123.1766689262865</v>
       </c>
       <c r="E50">
-        <v>11.36799999999999</v>
+        <v>12.70899999999999</v>
       </c>
       <c r="F50">
-        <v>64.36799999999999</v>
+        <v>65.70899999999999</v>
       </c>
       <c r="G50">
         <v>2.04</v>
@@ -5387,28 +5387,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M50">
-        <v>4.1259888</v>
+        <v>4.211946899999999</v>
       </c>
       <c r="N50">
-        <v>8.767344533333331</v>
+        <v>8.681386433333332</v>
       </c>
       <c r="O50">
-        <v>2.323346301333333</v>
+        <v>2.300567404833333</v>
       </c>
       <c r="P50">
-        <v>6.443998231999998</v>
+        <v>6.380819028499999</v>
       </c>
       <c r="Q50">
-        <v>10.883998232</v>
+        <v>10.8208190285</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09872423268027213</v>
+        <v>0.0995981231347032</v>
       </c>
       <c r="T50">
-        <v>1.222268653124068</v>
+        <v>1.242450880709081</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.124907496921303</v>
+        <v>3.061133874535154</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07388065779869864</v>
+        <v>0.07667673460365576</v>
       </c>
       <c r="C51">
-        <v>59.50766892628648</v>
+        <v>47.01226962475235</v>
       </c>
       <c r="D51">
-        <v>123.1766689262865</v>
+        <v>112.0222696247523</v>
       </c>
       <c r="E51">
-        <v>12.70899999999999</v>
+        <v>14.05</v>
       </c>
       <c r="F51">
-        <v>65.70899999999999</v>
+        <v>67.05</v>
       </c>
       <c r="G51">
         <v>2.04</v>
@@ -5469,45 +5469,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M51">
-        <v>4.211946899999999</v>
+        <v>4.820895</v>
       </c>
       <c r="N51">
-        <v>8.681386433333332</v>
+        <v>8.072438333333331</v>
       </c>
       <c r="O51">
-        <v>2.300567404833333</v>
+        <v>2.139196158333333</v>
       </c>
       <c r="P51">
-        <v>6.380819028499999</v>
+        <v>5.933242174999998</v>
       </c>
       <c r="Q51">
-        <v>10.8208190285</v>
+        <v>10.373242175</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0995981231347032</v>
+        <v>0.1005069692073115</v>
       </c>
       <c r="T51">
-        <v>1.242450880709081</v>
+        <v>1.263440397397495</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.265</v>
       </c>
       <c r="W51">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.061133874535154</v>
+        <v>2.674468814054928</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07667673460365576</v>
+        <v>0.0766636414086129</v>
       </c>
       <c r="C52">
-        <v>47.01226962475235</v>
+        <v>45.71879251441798</v>
       </c>
       <c r="D52">
-        <v>112.0222696247523</v>
+        <v>112.069792514418</v>
       </c>
       <c r="E52">
-        <v>14.05</v>
+        <v>15.39100000000001</v>
       </c>
       <c r="F52">
-        <v>67.05</v>
+        <v>68.39100000000001</v>
       </c>
       <c r="G52">
         <v>2.04</v>
@@ -5551,28 +5551,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M52">
-        <v>4.820895</v>
+        <v>4.917312900000001</v>
       </c>
       <c r="N52">
-        <v>8.072438333333331</v>
+        <v>7.97602043333333</v>
       </c>
       <c r="O52">
-        <v>2.139196158333333</v>
+        <v>2.113645414833333</v>
       </c>
       <c r="P52">
-        <v>5.933242174999998</v>
+        <v>5.862375018499998</v>
       </c>
       <c r="Q52">
-        <v>10.373242175</v>
+        <v>10.3023750185</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1005069692073115</v>
+        <v>0.1014529110379855</v>
       </c>
       <c r="T52">
-        <v>1.263440397397495</v>
+        <v>1.285286629052784</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.674468814054928</v>
+        <v>2.622028249073458</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0766636414086129</v>
+        <v>0.07665054821357004</v>
       </c>
       <c r="C53">
-        <v>45.71879251441798</v>
+        <v>44.42535574219748</v>
       </c>
       <c r="D53">
-        <v>112.069792514418</v>
+        <v>112.1173557421975</v>
       </c>
       <c r="E53">
-        <v>15.39100000000001</v>
+        <v>16.732</v>
       </c>
       <c r="F53">
-        <v>68.39100000000001</v>
+        <v>69.732</v>
       </c>
       <c r="G53">
         <v>2.04</v>
@@ -5633,28 +5633,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M53">
-        <v>4.917312900000001</v>
+        <v>5.0137308</v>
       </c>
       <c r="N53">
-        <v>7.97602043333333</v>
+        <v>7.879602533333331</v>
       </c>
       <c r="O53">
-        <v>2.113645414833333</v>
+        <v>2.088094671333333</v>
       </c>
       <c r="P53">
-        <v>5.862375018499998</v>
+        <v>5.791507861999998</v>
       </c>
       <c r="Q53">
-        <v>10.3023750185</v>
+        <v>10.231507862</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1014529110379855</v>
+        <v>0.1024382671116042</v>
       </c>
       <c r="T53">
-        <v>1.285286629052784</v>
+        <v>1.308043120360375</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.622028249073458</v>
+        <v>2.571604628898969</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07665054821357004</v>
+        <v>0.07663745501852716</v>
       </c>
       <c r="C54">
-        <v>44.42535574219748</v>
+        <v>43.13195935947205</v>
       </c>
       <c r="D54">
-        <v>112.1173557421975</v>
+        <v>112.164959359472</v>
       </c>
       <c r="E54">
-        <v>16.732</v>
+        <v>18.07300000000001</v>
       </c>
       <c r="F54">
-        <v>69.732</v>
+        <v>71.07300000000001</v>
       </c>
       <c r="G54">
         <v>2.04</v>
@@ -5715,28 +5715,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M54">
-        <v>5.0137308</v>
+        <v>5.110148700000001</v>
       </c>
       <c r="N54">
-        <v>7.879602533333331</v>
+        <v>7.78318463333333</v>
       </c>
       <c r="O54">
-        <v>2.088094671333333</v>
+        <v>2.062543927833333</v>
       </c>
       <c r="P54">
-        <v>5.791507861999998</v>
+        <v>5.720640705499997</v>
       </c>
       <c r="Q54">
-        <v>10.231507862</v>
+        <v>10.1606407055</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1024382671116042</v>
+        <v>0.1034655532309089</v>
       </c>
       <c r="T54">
-        <v>1.308043120360375</v>
+        <v>1.331767973000205</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.571604628898969</v>
+        <v>2.523083786844271</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07663745501852716</v>
+        <v>0.0781722718234843</v>
       </c>
       <c r="C55">
-        <v>43.13195935947205</v>
+        <v>36.47305441010842</v>
       </c>
       <c r="D55">
-        <v>112.164959359472</v>
+        <v>106.8470544101084</v>
       </c>
       <c r="E55">
-        <v>18.07300000000001</v>
+        <v>19.414</v>
       </c>
       <c r="F55">
-        <v>71.07300000000001</v>
+        <v>72.414</v>
       </c>
       <c r="G55">
         <v>2.04</v>
@@ -5797,45 +5797,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M55">
-        <v>5.110148700000001</v>
+        <v>5.4889812</v>
       </c>
       <c r="N55">
-        <v>7.78318463333333</v>
+        <v>7.40435213333333</v>
       </c>
       <c r="O55">
-        <v>2.062543927833333</v>
+        <v>1.962153315333333</v>
       </c>
       <c r="P55">
-        <v>5.720640705499997</v>
+        <v>5.442198817999998</v>
       </c>
       <c r="Q55">
-        <v>10.1606407055</v>
+        <v>9.882198817999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1034655532309089</v>
+        <v>0.1045375039640963</v>
       </c>
       <c r="T55">
-        <v>1.331767973000205</v>
+        <v>1.356524340972201</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.265</v>
       </c>
       <c r="W55">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.523083786844271</v>
+        <v>2.348948350075116</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0781722718234843</v>
+        <v>0.07818784362844144</v>
       </c>
       <c r="C56">
-        <v>36.47305441010842</v>
+        <v>35.08068323793015</v>
       </c>
       <c r="D56">
-        <v>106.8470544101084</v>
+        <v>106.7956832379301</v>
       </c>
       <c r="E56">
-        <v>19.414</v>
+        <v>20.75500000000001</v>
       </c>
       <c r="F56">
-        <v>72.414</v>
+        <v>73.75500000000001</v>
       </c>
       <c r="G56">
         <v>2.04</v>
@@ -5879,28 +5879,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M56">
-        <v>5.4889812</v>
+        <v>5.590629000000002</v>
       </c>
       <c r="N56">
-        <v>7.40435213333333</v>
+        <v>7.302704333333329</v>
       </c>
       <c r="O56">
-        <v>1.962153315333333</v>
+        <v>1.935216648333332</v>
       </c>
       <c r="P56">
-        <v>5.442198817999998</v>
+        <v>5.367487684999997</v>
       </c>
       <c r="Q56">
-        <v>9.882198817999999</v>
+        <v>9.807487684999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1045375039640963</v>
+        <v>0.1056570969520921</v>
       </c>
       <c r="T56">
-        <v>1.356524340972201</v>
+        <v>1.382380991965175</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.348948350075116</v>
+        <v>2.306240198255568</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07818784362844144</v>
+        <v>0.07820341543339857</v>
       </c>
       <c r="C57">
-        <v>35.08068323793015</v>
+        <v>33.68836143967522</v>
       </c>
       <c r="D57">
-        <v>106.7956832379301</v>
+        <v>106.7443614396752</v>
       </c>
       <c r="E57">
-        <v>20.75500000000001</v>
+        <v>22.096</v>
       </c>
       <c r="F57">
-        <v>73.75500000000001</v>
+        <v>75.096</v>
       </c>
       <c r="G57">
         <v>2.04</v>
@@ -5961,28 +5961,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M57">
-        <v>5.590629000000002</v>
+        <v>5.692276800000001</v>
       </c>
       <c r="N57">
-        <v>7.302704333333329</v>
+        <v>7.20105653333333</v>
       </c>
       <c r="O57">
-        <v>1.935216648333332</v>
+        <v>1.908279981333332</v>
       </c>
       <c r="P57">
-        <v>5.367487684999997</v>
+        <v>5.292776551999998</v>
       </c>
       <c r="Q57">
-        <v>9.807487684999998</v>
+        <v>9.732776551999997</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1056570969520921</v>
+        <v>0.1068275805304513</v>
       </c>
       <c r="T57">
-        <v>1.382380991965175</v>
+        <v>1.409412945276011</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.306240198255568</v>
+        <v>2.265057337572433</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07820341543339857</v>
+        <v>0.0782189872383557</v>
       </c>
       <c r="C58">
-        <v>33.68836143967522</v>
+        <v>32.2960889441962</v>
       </c>
       <c r="D58">
-        <v>106.7443614396752</v>
+        <v>106.6930889441962</v>
       </c>
       <c r="E58">
-        <v>22.096</v>
+        <v>23.43700000000001</v>
       </c>
       <c r="F58">
-        <v>75.096</v>
+        <v>76.43700000000001</v>
       </c>
       <c r="G58">
         <v>2.04</v>
@@ -6043,28 +6043,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M58">
-        <v>5.692276800000001</v>
+        <v>5.793924600000001</v>
       </c>
       <c r="N58">
-        <v>7.20105653333333</v>
+        <v>7.09940873333333</v>
       </c>
       <c r="O58">
-        <v>1.908279981333332</v>
+        <v>1.881343314333332</v>
       </c>
       <c r="P58">
-        <v>5.292776551999998</v>
+        <v>5.218065418999997</v>
       </c>
       <c r="Q58">
-        <v>9.732776551999997</v>
+        <v>9.658065418999996</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1068275805304513</v>
+        <v>0.1080525052054784</v>
       </c>
       <c r="T58">
-        <v>1.409412945276011</v>
+        <v>1.43770219874084</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.265057337572433</v>
+        <v>2.225319489544846</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0782189872383557</v>
+        <v>0.07823455904331283</v>
       </c>
       <c r="C59">
-        <v>32.2960889441962</v>
+        <v>30.9038656804825</v>
       </c>
       <c r="D59">
-        <v>106.6930889441962</v>
+        <v>106.6418656804825</v>
       </c>
       <c r="E59">
-        <v>23.43700000000001</v>
+        <v>24.77800000000001</v>
       </c>
       <c r="F59">
-        <v>76.43700000000001</v>
+        <v>77.77800000000001</v>
       </c>
       <c r="G59">
         <v>2.04</v>
@@ -6125,28 +6125,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M59">
-        <v>5.793924600000001</v>
+        <v>5.895572400000001</v>
       </c>
       <c r="N59">
-        <v>7.09940873333333</v>
+        <v>6.99776093333333</v>
       </c>
       <c r="O59">
-        <v>1.881343314333332</v>
+        <v>1.854406647333332</v>
       </c>
       <c r="P59">
-        <v>5.218065418999997</v>
+        <v>5.143354285999997</v>
       </c>
       <c r="Q59">
-        <v>9.658065418999996</v>
+        <v>9.583354285999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1080525052054784</v>
+        <v>0.1093357596269353</v>
       </c>
       <c r="T59">
-        <v>1.43770219874084</v>
+        <v>1.467338559513518</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.225319489544846</v>
+        <v>2.186951912138901</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07823455904331283</v>
+        <v>0.07825013084826997</v>
       </c>
       <c r="C60">
-        <v>30.90386568048251</v>
+        <v>29.51169157765976</v>
       </c>
       <c r="D60">
-        <v>106.6418656804825</v>
+        <v>106.5906915776597</v>
       </c>
       <c r="E60">
-        <v>24.77799999999999</v>
+        <v>26.11899999999999</v>
       </c>
       <c r="F60">
-        <v>77.77799999999999</v>
+        <v>79.11899999999999</v>
       </c>
       <c r="G60">
         <v>2.04</v>
@@ -6207,28 +6207,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M60">
-        <v>5.8955724</v>
+        <v>5.997220199999999</v>
       </c>
       <c r="N60">
-        <v>6.997760933333331</v>
+        <v>6.896113133333332</v>
       </c>
       <c r="O60">
-        <v>1.854406647333333</v>
+        <v>1.827469980333333</v>
       </c>
       <c r="P60">
-        <v>5.143354285999998</v>
+        <v>5.068643152999998</v>
       </c>
       <c r="Q60">
-        <v>9.583354285999999</v>
+        <v>9.508643152999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1093357596269353</v>
+        <v>0.1106816118250487</v>
       </c>
       <c r="T60">
-        <v>1.467338559513517</v>
+        <v>1.498420596421448</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.186951912138901</v>
+        <v>2.149884930577225</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07825013084826997</v>
+        <v>0.0782657026532271</v>
       </c>
       <c r="C61">
-        <v>29.51169157765976</v>
+        <v>28.11956656498955</v>
       </c>
       <c r="D61">
-        <v>106.5906915776597</v>
+        <v>106.5395665649895</v>
       </c>
       <c r="E61">
-        <v>26.11899999999999</v>
+        <v>27.45999999999999</v>
       </c>
       <c r="F61">
-        <v>79.11899999999999</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="G61">
         <v>2.04</v>
@@ -6289,28 +6289,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M61">
-        <v>5.997220199999999</v>
+        <v>6.098868</v>
       </c>
       <c r="N61">
-        <v>6.896113133333332</v>
+        <v>6.79446533333333</v>
       </c>
       <c r="O61">
-        <v>1.827469980333333</v>
+        <v>1.800533313333333</v>
       </c>
       <c r="P61">
-        <v>5.068643152999998</v>
+        <v>4.993932019999997</v>
       </c>
       <c r="Q61">
-        <v>9.508643152999998</v>
+        <v>9.433932019999997</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1106816118250487</v>
+        <v>0.1120947566330677</v>
       </c>
       <c r="T61">
-        <v>1.498420596421448</v>
+        <v>1.531056735174775</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.149884930577225</v>
+        <v>2.114053515067604</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0782657026532271</v>
+        <v>0.07828127445818422</v>
       </c>
       <c r="C62">
-        <v>28.11956656498955</v>
+        <v>26.72749057186921</v>
       </c>
       <c r="D62">
-        <v>106.5395665649895</v>
+        <v>106.4884905718692</v>
       </c>
       <c r="E62">
-        <v>27.45999999999999</v>
+        <v>28.80099999999999</v>
       </c>
       <c r="F62">
-        <v>80.45999999999999</v>
+        <v>81.80099999999999</v>
       </c>
       <c r="G62">
         <v>2.04</v>
@@ -6371,28 +6371,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M62">
-        <v>6.098868</v>
+        <v>6.2005158</v>
       </c>
       <c r="N62">
-        <v>6.79446533333333</v>
+        <v>6.692817533333331</v>
       </c>
       <c r="O62">
-        <v>1.800533313333333</v>
+        <v>1.773596646333333</v>
       </c>
       <c r="P62">
-        <v>4.993932019999997</v>
+        <v>4.919220886999998</v>
       </c>
       <c r="Q62">
-        <v>9.433932019999997</v>
+        <v>9.359220886999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1120947566330677</v>
+        <v>0.1135803704056006</v>
       </c>
       <c r="T62">
-        <v>1.531056735174775</v>
+        <v>1.565366522069298</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.114053515067604</v>
+        <v>2.079396900066496</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07828127445818422</v>
+        <v>0.07829684626314137</v>
       </c>
       <c r="C63">
-        <v>26.72749057186921</v>
+        <v>25.33546352783118</v>
       </c>
       <c r="D63">
-        <v>106.4884905718692</v>
+        <v>106.4374635278312</v>
       </c>
       <c r="E63">
-        <v>28.80099999999999</v>
+        <v>30.142</v>
       </c>
       <c r="F63">
-        <v>81.80099999999999</v>
+        <v>83.142</v>
       </c>
       <c r="G63">
         <v>2.04</v>
@@ -6453,28 +6453,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M63">
-        <v>6.2005158</v>
+        <v>6.3021636</v>
       </c>
       <c r="N63">
-        <v>6.692817533333331</v>
+        <v>6.591169733333331</v>
       </c>
       <c r="O63">
-        <v>1.773596646333333</v>
+        <v>1.746659979333333</v>
       </c>
       <c r="P63">
-        <v>4.919220886999998</v>
+        <v>4.844509753999998</v>
       </c>
       <c r="Q63">
-        <v>9.359220886999999</v>
+        <v>9.284509753999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1135803704056006</v>
+        <v>0.1151441743766878</v>
       </c>
       <c r="T63">
-        <v>1.565366522069298</v>
+        <v>1.601482087221427</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.079396900066496</v>
+        <v>2.045858240388005</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07829684626314137</v>
+        <v>0.07831241806809849</v>
       </c>
       <c r="C64">
-        <v>25.33546352783118</v>
+        <v>23.94348536254324</v>
       </c>
       <c r="D64">
-        <v>106.4374635278312</v>
+        <v>106.3864853625432</v>
       </c>
       <c r="E64">
-        <v>30.142</v>
+        <v>31.483</v>
       </c>
       <c r="F64">
-        <v>83.142</v>
+        <v>84.483</v>
       </c>
       <c r="G64">
         <v>2.04</v>
@@ -6535,28 +6535,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M64">
-        <v>6.3021636</v>
+        <v>6.403811400000001</v>
       </c>
       <c r="N64">
-        <v>6.591169733333331</v>
+        <v>6.48952193333333</v>
       </c>
       <c r="O64">
-        <v>1.746659979333333</v>
+        <v>1.719723312333332</v>
       </c>
       <c r="P64">
-        <v>4.844509753999998</v>
+        <v>4.769798620999997</v>
       </c>
       <c r="Q64">
-        <v>9.284509753999998</v>
+        <v>9.209798620999997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1151441743766878</v>
+        <v>0.1167925082921581</v>
       </c>
       <c r="T64">
-        <v>1.601482087221427</v>
+        <v>1.639549845084483</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.045858240388005</v>
+        <v>2.013384300064385</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07831241806809849</v>
+        <v>0.08500766987305561</v>
       </c>
       <c r="C65">
-        <v>23.94348536254324</v>
+        <v>4.435521846149499</v>
       </c>
       <c r="D65">
-        <v>106.3864853625432</v>
+        <v>88.21952184614949</v>
       </c>
       <c r="E65">
-        <v>31.483</v>
+        <v>32.824</v>
       </c>
       <c r="F65">
-        <v>84.483</v>
+        <v>85.824</v>
       </c>
       <c r="G65">
         <v>2.04</v>
@@ -6617,45 +6617,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M65">
-        <v>6.403811400000001</v>
+        <v>7.724159999999999</v>
       </c>
       <c r="N65">
-        <v>6.48952193333333</v>
+        <v>5.169173333333331</v>
       </c>
       <c r="O65">
-        <v>1.719723312333332</v>
+        <v>1.369830933333333</v>
       </c>
       <c r="P65">
-        <v>4.769798620999997</v>
+        <v>3.799342399999999</v>
       </c>
       <c r="Q65">
-        <v>9.209798620999997</v>
+        <v>8.239342399999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1167925082921581</v>
+        <v>0.1185324163140434</v>
       </c>
       <c r="T65">
-        <v>1.639549845084483</v>
+        <v>1.679732478384374</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.265</v>
       </c>
       <c r="W65">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.013384300064385</v>
+        <v>1.669221421272129</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08500766987305561</v>
+        <v>0.08512761167801275</v>
       </c>
       <c r="C66">
-        <v>4.435521846149499</v>
+        <v>2.825468928079744</v>
       </c>
       <c r="D66">
-        <v>88.21952184614949</v>
+        <v>87.95046892807974</v>
       </c>
       <c r="E66">
-        <v>32.824</v>
+        <v>34.16500000000001</v>
       </c>
       <c r="F66">
-        <v>85.824</v>
+        <v>87.16500000000001</v>
       </c>
       <c r="G66">
         <v>2.04</v>
@@ -6699,28 +6699,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M66">
-        <v>7.724159999999999</v>
+        <v>7.84485</v>
       </c>
       <c r="N66">
-        <v>5.169173333333331</v>
+        <v>5.048483333333331</v>
       </c>
       <c r="O66">
-        <v>1.369830933333333</v>
+        <v>1.337848083333333</v>
       </c>
       <c r="P66">
-        <v>3.799342399999999</v>
+        <v>3.710635249999998</v>
       </c>
       <c r="Q66">
-        <v>8.239342399999998</v>
+        <v>8.150635249999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1185324163140434</v>
+        <v>0.120371747651465</v>
       </c>
       <c r="T66">
-        <v>1.679732478384374</v>
+        <v>1.722211262158546</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.669221421272129</v>
+        <v>1.643541091714097</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08512761167801275</v>
+        <v>0.08524755348296989</v>
       </c>
       <c r="C67">
-        <v>2.825468928079744</v>
+        <v>1.217052141519986</v>
       </c>
       <c r="D67">
-        <v>87.95046892807974</v>
+        <v>87.68305214151998</v>
       </c>
       <c r="E67">
-        <v>34.16500000000001</v>
+        <v>35.506</v>
       </c>
       <c r="F67">
-        <v>87.16500000000001</v>
+        <v>88.506</v>
       </c>
       <c r="G67">
         <v>2.04</v>
@@ -6781,28 +6781,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M67">
-        <v>7.84485</v>
+        <v>7.96554</v>
       </c>
       <c r="N67">
-        <v>5.048483333333331</v>
+        <v>4.927793333333331</v>
       </c>
       <c r="O67">
-        <v>1.337848083333333</v>
+        <v>1.305865233333333</v>
       </c>
       <c r="P67">
-        <v>3.710635249999998</v>
+        <v>3.621928099999998</v>
       </c>
       <c r="Q67">
-        <v>8.150635249999999</v>
+        <v>8.061928099999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.120371747651465</v>
+        <v>0.1223192749499114</v>
       </c>
       <c r="T67">
-        <v>1.722211262158546</v>
+        <v>1.767188797919433</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.643541091714097</v>
+        <v>1.618638953960853</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08524755348296989</v>
+        <v>0.08536749528792703</v>
       </c>
       <c r="C68">
-        <v>1.217052141519986</v>
+        <v>-0.3897433924524307</v>
       </c>
       <c r="D68">
-        <v>87.68305214151998</v>
+        <v>87.41725660754757</v>
       </c>
       <c r="E68">
-        <v>35.506</v>
+        <v>36.84700000000001</v>
       </c>
       <c r="F68">
-        <v>88.506</v>
+        <v>89.84700000000001</v>
       </c>
       <c r="G68">
         <v>2.04</v>
@@ -6863,28 +6863,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M68">
-        <v>7.96554</v>
+        <v>8.08623</v>
       </c>
       <c r="N68">
-        <v>4.927793333333331</v>
+        <v>4.80710333333333</v>
       </c>
       <c r="O68">
-        <v>1.305865233333333</v>
+        <v>1.273882383333333</v>
       </c>
       <c r="P68">
-        <v>3.621928099999998</v>
+        <v>3.533220949999998</v>
       </c>
       <c r="Q68">
-        <v>8.061928099999999</v>
+        <v>7.973220949999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1223192749499114</v>
+        <v>0.1243848342058395</v>
       </c>
       <c r="T68">
-        <v>1.767188797919433</v>
+        <v>1.814892244938556</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.618638953960853</v>
+        <v>1.594480163603228</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08536749528792703</v>
+        <v>0.08548743709288414</v>
       </c>
       <c r="C69">
-        <v>-0.3897433924524307</v>
+        <v>-1.994932372894013</v>
       </c>
       <c r="D69">
-        <v>87.41725660754757</v>
+        <v>87.15306762710598</v>
       </c>
       <c r="E69">
-        <v>36.84700000000001</v>
+        <v>38.188</v>
       </c>
       <c r="F69">
-        <v>89.84700000000001</v>
+        <v>91.188</v>
       </c>
       <c r="G69">
         <v>2.04</v>
@@ -6945,28 +6945,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M69">
-        <v>8.08623</v>
+        <v>8.20692</v>
       </c>
       <c r="N69">
-        <v>4.80710333333333</v>
+        <v>4.686413333333331</v>
       </c>
       <c r="O69">
-        <v>1.273882383333333</v>
+        <v>1.241899533333333</v>
       </c>
       <c r="P69">
-        <v>3.533220949999998</v>
+        <v>3.444513799999998</v>
       </c>
       <c r="Q69">
-        <v>7.973220949999998</v>
+        <v>7.884513799999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1243848342058395</v>
+        <v>0.126579490915263</v>
       </c>
       <c r="T69">
-        <v>1.814892244938556</v>
+        <v>1.865577157396374</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.594480163603228</v>
+        <v>1.57103192590318</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08548743709288414</v>
+        <v>0.08560737889784129</v>
       </c>
       <c r="C70">
-        <v>-1.994932372894013</v>
+        <v>-3.598529321705271</v>
       </c>
       <c r="D70">
-        <v>87.15306762710598</v>
+        <v>86.89047067829473</v>
       </c>
       <c r="E70">
-        <v>38.188</v>
+        <v>39.52900000000001</v>
       </c>
       <c r="F70">
-        <v>91.188</v>
+        <v>92.52900000000001</v>
       </c>
       <c r="G70">
         <v>2.04</v>
@@ -7027,28 +7027,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M70">
-        <v>8.20692</v>
+        <v>8.32761</v>
       </c>
       <c r="N70">
-        <v>4.686413333333331</v>
+        <v>4.565723333333331</v>
       </c>
       <c r="O70">
-        <v>1.241899533333333</v>
+        <v>1.209916683333333</v>
       </c>
       <c r="P70">
-        <v>3.444513799999998</v>
+        <v>3.355806649999998</v>
       </c>
       <c r="Q70">
-        <v>7.884513799999999</v>
+        <v>7.795806649999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.126579490915263</v>
+        <v>0.1289157383801332</v>
       </c>
       <c r="T70">
-        <v>1.865577157396374</v>
+        <v>1.91953206420631</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.57103192590318</v>
+        <v>1.548263347266903</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08560737889784129</v>
+        <v>0.08572732070279843</v>
       </c>
       <c r="C71">
-        <v>-3.598529321705271</v>
+        <v>-5.200548586291177</v>
       </c>
       <c r="D71">
-        <v>86.89047067829473</v>
+        <v>86.62945141370882</v>
       </c>
       <c r="E71">
-        <v>39.52900000000001</v>
+        <v>40.87</v>
       </c>
       <c r="F71">
-        <v>92.52900000000001</v>
+        <v>93.87</v>
       </c>
       <c r="G71">
         <v>2.04</v>
@@ -7109,28 +7109,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M71">
-        <v>8.32761</v>
+        <v>8.4483</v>
       </c>
       <c r="N71">
-        <v>4.565723333333331</v>
+        <v>4.445033333333331</v>
       </c>
       <c r="O71">
-        <v>1.209916683333333</v>
+        <v>1.177933833333333</v>
       </c>
       <c r="P71">
-        <v>3.355806649999998</v>
+        <v>3.267099499999998</v>
       </c>
       <c r="Q71">
-        <v>7.795806649999999</v>
+        <v>7.707099499999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1289157383801332</v>
+        <v>0.1314077356759947</v>
       </c>
       <c r="T71">
-        <v>1.91953206420631</v>
+        <v>1.977083964803574</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.548263347266903</v>
+        <v>1.526145299448804</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08572732070279843</v>
+        <v>0.08584726250775555</v>
       </c>
       <c r="C72">
-        <v>-5.200548586291177</v>
+        <v>-6.80100434217448</v>
       </c>
       <c r="D72">
-        <v>86.62945141370882</v>
+        <v>86.36999565782553</v>
       </c>
       <c r="E72">
-        <v>40.87</v>
+        <v>42.21100000000001</v>
       </c>
       <c r="F72">
-        <v>93.87</v>
+        <v>95.21100000000001</v>
       </c>
       <c r="G72">
         <v>2.04</v>
@@ -7191,28 +7191,28 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M72">
-        <v>8.4483</v>
+        <v>8.568990000000001</v>
       </c>
       <c r="N72">
-        <v>4.445033333333331</v>
+        <v>4.32434333333333</v>
       </c>
       <c r="O72">
-        <v>1.177933833333333</v>
+        <v>1.145950983333332</v>
       </c>
       <c r="P72">
-        <v>3.267099499999998</v>
+        <v>3.178392349999998</v>
       </c>
       <c r="Q72">
-        <v>7.707099499999998</v>
+        <v>7.618392349999998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1314077356759947</v>
+        <v>0.1340715948543295</v>
       </c>
       <c r="T72">
-        <v>1.977083964803574</v>
+        <v>2.038604961993753</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.526145299448804</v>
+        <v>1.504650295231215</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08584726250775554</v>
+        <v>0.1190997264864801</v>
       </c>
       <c r="C73">
-        <v>-6.801004342174423</v>
+        <v>-47.32380360829004</v>
       </c>
       <c r="D73">
-        <v>86.36999565782556</v>
+        <v>47.18819639170995</v>
       </c>
       <c r="E73">
-        <v>42.21099999999998</v>
+        <v>43.55199999999999</v>
       </c>
       <c r="F73">
-        <v>95.21099999999998</v>
+        <v>96.55199999999999</v>
       </c>
       <c r="G73">
         <v>2.04</v>
@@ -7273,45 +7273,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M73">
-        <v>8.568989999999998</v>
+        <v>14.1738336</v>
       </c>
       <c r="N73">
-        <v>4.324343333333333</v>
+        <v>-1.280500266666669</v>
       </c>
       <c r="O73">
-        <v>1.145950983333333</v>
+        <v>-0.3393325706666673</v>
       </c>
       <c r="P73">
-        <v>3.17839235</v>
+        <v>-0.9411676960000018</v>
       </c>
       <c r="Q73">
-        <v>7.618392350000001</v>
+        <v>3.498832303999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1340715948543295</v>
+        <v>0.1388668652170638</v>
       </c>
       <c r="T73">
-        <v>2.038604961993752</v>
+        <v>2.149350235959905</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.265</v>
+        <v>0.2410592243254029</v>
       </c>
       <c r="W73">
-        <v>0.06615</v>
+        <v>0.1114125058690309</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.504650295231216</v>
+        <v>0.9096574502845391</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1190997264864801</v>
+        <v>0.1201097264864801</v>
       </c>
       <c r="C74">
-        <v>-47.32380360829004</v>
+        <v>-49.30617426875532</v>
       </c>
       <c r="D74">
-        <v>47.18819639170995</v>
+        <v>46.54682573124467</v>
       </c>
       <c r="E74">
-        <v>43.55199999999999</v>
+        <v>44.89299999999999</v>
       </c>
       <c r="F74">
-        <v>96.55199999999999</v>
+        <v>97.89299999999999</v>
       </c>
       <c r="G74">
         <v>2.04</v>
@@ -7355,37 +7355,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M74">
-        <v>14.1738336</v>
+        <v>14.3706924</v>
       </c>
       <c r="N74">
-        <v>-1.280500266666669</v>
+        <v>-1.477359066666668</v>
       </c>
       <c r="O74">
-        <v>-0.3393325706666673</v>
+        <v>-0.3915001526666672</v>
       </c>
       <c r="P74">
-        <v>-0.9411676960000018</v>
+        <v>-1.085858914000001</v>
       </c>
       <c r="Q74">
-        <v>3.498832303999999</v>
+        <v>3.354141085999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1388668652170638</v>
+        <v>0.1423137861510292</v>
       </c>
       <c r="T74">
-        <v>2.149350235959905</v>
+        <v>2.228955800254716</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2410592243254029</v>
+        <v>0.2377570431702604</v>
       </c>
       <c r="W74">
-        <v>0.1114125058690309</v>
+        <v>0.1118972660626058</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9096574502845391</v>
+        <v>0.8971963893217373</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1201097264864801</v>
+        <v>0.1211197264864801</v>
       </c>
       <c r="C75">
-        <v>-49.30617426875532</v>
+        <v>-51.2713440073031</v>
       </c>
       <c r="D75">
-        <v>46.54682573124467</v>
+        <v>45.9226559926969</v>
       </c>
       <c r="E75">
-        <v>44.89299999999999</v>
+        <v>46.23399999999999</v>
       </c>
       <c r="F75">
-        <v>97.89299999999999</v>
+        <v>99.23399999999999</v>
       </c>
       <c r="G75">
         <v>2.04</v>
@@ -7437,37 +7437,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M75">
-        <v>14.3706924</v>
+        <v>14.5675512</v>
       </c>
       <c r="N75">
-        <v>-1.477359066666668</v>
+        <v>-1.67421786666667</v>
       </c>
       <c r="O75">
-        <v>-0.3915001526666672</v>
+        <v>-0.4436677346666675</v>
       </c>
       <c r="P75">
-        <v>-1.085858914000001</v>
+        <v>-1.230550132000002</v>
       </c>
       <c r="Q75">
-        <v>3.354141085999999</v>
+        <v>3.209449867999998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1423137861510292</v>
+        <v>0.1460258548491457</v>
       </c>
       <c r="T75">
-        <v>2.228955800254716</v>
+        <v>2.314684869495282</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2377570431702604</v>
+        <v>0.2345441101544461</v>
       </c>
       <c r="W75">
-        <v>0.1118972660626058</v>
+        <v>0.1123689246293273</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8971963893217373</v>
+        <v>0.8850721137903624</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1211197264864801</v>
+        <v>0.1221297264864801</v>
       </c>
       <c r="C76">
-        <v>-51.2713440073031</v>
+        <v>-53.21999563515008</v>
       </c>
       <c r="D76">
-        <v>45.9226559926969</v>
+        <v>45.31500436484991</v>
       </c>
       <c r="E76">
-        <v>46.23399999999999</v>
+        <v>47.57499999999999</v>
       </c>
       <c r="F76">
-        <v>99.23399999999999</v>
+        <v>100.575</v>
       </c>
       <c r="G76">
         <v>2.04</v>
@@ -7519,37 +7519,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M76">
-        <v>14.5675512</v>
+        <v>14.76441</v>
       </c>
       <c r="N76">
-        <v>-1.67421786666667</v>
+        <v>-1.871076666666669</v>
       </c>
       <c r="O76">
-        <v>-0.4436677346666675</v>
+        <v>-0.4958353166666673</v>
       </c>
       <c r="P76">
-        <v>-1.230550132000002</v>
+        <v>-1.375241350000002</v>
       </c>
       <c r="Q76">
-        <v>3.209449867999998</v>
+        <v>3.064758649999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1460258548491457</v>
+        <v>0.1500348890431115</v>
       </c>
       <c r="T76">
-        <v>2.314684869495282</v>
+        <v>2.407272264275093</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2345441101544461</v>
+        <v>0.2314168553523868</v>
       </c>
       <c r="W76">
-        <v>0.1123689246293273</v>
+        <v>0.1128280056342696</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8850721137903624</v>
+        <v>0.8732711522731575</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1221297264864801</v>
+        <v>0.1231397264864801</v>
       </c>
       <c r="C77">
-        <v>-53.21999563515008</v>
+        <v>-55.15277629546183</v>
       </c>
       <c r="D77">
-        <v>45.31500436484991</v>
+        <v>44.72322370453816</v>
       </c>
       <c r="E77">
-        <v>47.57499999999999</v>
+        <v>48.916</v>
       </c>
       <c r="F77">
-        <v>100.575</v>
+        <v>101.916</v>
       </c>
       <c r="G77">
         <v>2.04</v>
@@ -7601,37 +7601,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M77">
-        <v>14.76441</v>
+        <v>14.9612688</v>
       </c>
       <c r="N77">
-        <v>-1.871076666666669</v>
+        <v>-2.06793546666667</v>
       </c>
       <c r="O77">
-        <v>-0.4958353166666673</v>
+        <v>-0.5480028986666676</v>
       </c>
       <c r="P77">
-        <v>-1.375241350000002</v>
+        <v>-1.519932568000002</v>
       </c>
       <c r="Q77">
-        <v>3.064758649999999</v>
+        <v>2.920067431999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1500348890431115</v>
+        <v>0.1543780094199078</v>
       </c>
       <c r="T77">
-        <v>2.407272264275093</v>
+        <v>2.507575275286555</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2314168553523868</v>
+        <v>0.228371896729329</v>
       </c>
       <c r="W77">
-        <v>0.1128280056342696</v>
+        <v>0.1132750055601345</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8732711522731575</v>
+        <v>0.8617807423748265</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1231397264864801</v>
+        <v>0.1241497264864801</v>
       </c>
       <c r="C78">
-        <v>-55.15277629546183</v>
+        <v>-57.07029976232266</v>
       </c>
       <c r="D78">
-        <v>44.72322370453816</v>
+        <v>44.14670023767735</v>
       </c>
       <c r="E78">
-        <v>48.916</v>
+        <v>50.25700000000001</v>
       </c>
       <c r="F78">
-        <v>101.916</v>
+        <v>103.257</v>
       </c>
       <c r="G78">
         <v>2.04</v>
@@ -7683,37 +7683,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M78">
-        <v>14.9612688</v>
+        <v>15.1581276</v>
       </c>
       <c r="N78">
-        <v>-2.06793546666667</v>
+        <v>-2.264794266666671</v>
       </c>
       <c r="O78">
-        <v>-0.5480028986666676</v>
+        <v>-0.6001704806666679</v>
       </c>
       <c r="P78">
-        <v>-1.519932568000002</v>
+        <v>-1.664623786000003</v>
       </c>
       <c r="Q78">
-        <v>2.920067431999998</v>
+        <v>2.775376213999997</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1543780094199078</v>
+        <v>0.1590987924381647</v>
       </c>
       <c r="T78">
-        <v>2.507575275286555</v>
+        <v>2.616600287255536</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.228371896729329</v>
+        <v>0.2254060279406364</v>
       </c>
       <c r="W78">
-        <v>0.1132750055601345</v>
+        <v>0.1137103950983146</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8617807423748265</v>
+        <v>0.8505887846816469</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1241497264864801</v>
+        <v>0.1251597264864801</v>
       </c>
       <c r="C79">
-        <v>-57.07029976232266</v>
+        <v>-58.97314856415353</v>
       </c>
       <c r="D79">
-        <v>44.14670023767735</v>
+        <v>43.58485143584647</v>
       </c>
       <c r="E79">
-        <v>50.25700000000001</v>
+        <v>51.598</v>
       </c>
       <c r="F79">
-        <v>103.257</v>
+        <v>104.598</v>
       </c>
       <c r="G79">
         <v>2.04</v>
@@ -7765,37 +7765,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M79">
-        <v>15.1581276</v>
+        <v>15.3549864</v>
       </c>
       <c r="N79">
-        <v>-2.264794266666671</v>
+        <v>-2.46165306666667</v>
       </c>
       <c r="O79">
-        <v>-0.6001704806666679</v>
+        <v>-0.6523380626666677</v>
       </c>
       <c r="P79">
-        <v>-1.664623786000003</v>
+        <v>-1.809315004000003</v>
       </c>
       <c r="Q79">
-        <v>2.775376213999997</v>
+        <v>2.630684995999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1590987924381647</v>
+        <v>0.1642487375489904</v>
       </c>
       <c r="T79">
-        <v>2.616600287255536</v>
+        <v>2.73553666394897</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2254060279406364</v>
+        <v>0.2225162070696027</v>
       </c>
       <c r="W79">
-        <v>0.1137103950983146</v>
+        <v>0.1141346208021823</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8505887846816469</v>
+        <v>0.8396838002626514</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1251597264864801</v>
+        <v>0.1261697264864801</v>
       </c>
       <c r="C80">
-        <v>-58.97314856415353</v>
+        <v>-60.86187594702088</v>
       </c>
       <c r="D80">
-        <v>43.58485143584647</v>
+        <v>43.03712405297912</v>
       </c>
       <c r="E80">
-        <v>51.598</v>
+        <v>52.93900000000001</v>
       </c>
       <c r="F80">
-        <v>104.598</v>
+        <v>105.939</v>
       </c>
       <c r="G80">
         <v>2.04</v>
@@ -7847,37 +7847,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M80">
-        <v>15.3549864</v>
+        <v>15.5518452</v>
       </c>
       <c r="N80">
-        <v>-2.46165306666667</v>
+        <v>-2.658511866666672</v>
       </c>
       <c r="O80">
-        <v>-0.6523380626666677</v>
+        <v>-0.704505644666668</v>
       </c>
       <c r="P80">
-        <v>-1.809315004000003</v>
+        <v>-1.954006222000004</v>
       </c>
       <c r="Q80">
-        <v>2.630684995999998</v>
+        <v>2.485993777999997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1642487375489904</v>
+        <v>0.1698891536227518</v>
       </c>
       <c r="T80">
-        <v>2.73553666394897</v>
+        <v>2.865800314613206</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2225162070696027</v>
+        <v>0.2196995462206203</v>
       </c>
       <c r="W80">
-        <v>0.1141346208021823</v>
+        <v>0.1145481066148129</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8396838002626514</v>
+        <v>0.8290548913985673</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1261697264864801</v>
+        <v>0.1271797264864801</v>
       </c>
       <c r="C81">
-        <v>-60.86187594702088</v>
+        <v>-62.73700769174641</v>
       </c>
       <c r="D81">
-        <v>43.03712405297912</v>
+        <v>42.50299230825359</v>
       </c>
       <c r="E81">
-        <v>52.93900000000001</v>
+        <v>54.28</v>
       </c>
       <c r="F81">
-        <v>105.939</v>
+        <v>107.28</v>
       </c>
       <c r="G81">
         <v>2.04</v>
@@ -7929,37 +7929,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M81">
-        <v>15.5518452</v>
+        <v>15.748704</v>
       </c>
       <c r="N81">
-        <v>-2.658511866666672</v>
+        <v>-2.855370666666671</v>
       </c>
       <c r="O81">
-        <v>-0.704505644666668</v>
+        <v>-0.7566732266666678</v>
       </c>
       <c r="P81">
-        <v>-1.954006222000004</v>
+        <v>-2.098697440000003</v>
       </c>
       <c r="Q81">
-        <v>2.485993777999997</v>
+        <v>2.341302559999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1698891536227518</v>
+        <v>0.1760936113038894</v>
       </c>
       <c r="T81">
-        <v>2.865800314613206</v>
+        <v>3.009090330343867</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2196995462206203</v>
+        <v>0.2169533018928626</v>
       </c>
       <c r="W81">
-        <v>0.1145481066148129</v>
+        <v>0.1149512552821278</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8290548913985673</v>
+        <v>0.8186917052560851</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1271797264864801</v>
+        <v>0.1281897264864801</v>
       </c>
       <c r="C82">
-        <v>-62.73700769174641</v>
+        <v>-64.59904379736307</v>
       </c>
       <c r="D82">
-        <v>42.50299230825359</v>
+        <v>41.98195620263694</v>
       </c>
       <c r="E82">
-        <v>54.28</v>
+        <v>55.62100000000001</v>
       </c>
       <c r="F82">
-        <v>107.28</v>
+        <v>108.621</v>
       </c>
       <c r="G82">
         <v>2.04</v>
@@ -8011,37 +8011,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M82">
-        <v>15.748704</v>
+        <v>15.9455628</v>
       </c>
       <c r="N82">
-        <v>-2.855370666666671</v>
+        <v>-3.052229466666672</v>
       </c>
       <c r="O82">
-        <v>-0.7566732266666678</v>
+        <v>-0.8088408086666682</v>
       </c>
       <c r="P82">
-        <v>-2.098697440000003</v>
+        <v>-2.243388658000004</v>
       </c>
       <c r="Q82">
-        <v>2.341302559999997</v>
+        <v>2.196611341999997</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1760936113038894</v>
+        <v>0.1829511697935678</v>
       </c>
       <c r="T82">
-        <v>3.009090330343867</v>
+        <v>3.167463505625124</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2169533018928626</v>
+        <v>0.2142748660670248</v>
       </c>
       <c r="W82">
-        <v>0.1149512552821278</v>
+        <v>0.1153444496613608</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8186917052560851</v>
+        <v>0.8085844002529236</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1281897264864801</v>
+        <v>0.1749514610140257</v>
       </c>
       <c r="C83">
-        <v>-64.59904379736307</v>
+        <v>-81.14040680898674</v>
       </c>
       <c r="D83">
-        <v>41.98195620263694</v>
+        <v>26.78159319101327</v>
       </c>
       <c r="E83">
-        <v>55.62100000000001</v>
+        <v>56.962</v>
       </c>
       <c r="F83">
-        <v>108.621</v>
+        <v>109.962</v>
       </c>
       <c r="G83">
         <v>2.04</v>
@@ -8093,45 +8093,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M83">
-        <v>15.9455628</v>
+        <v>22.0803696</v>
       </c>
       <c r="N83">
-        <v>-3.052229466666672</v>
+        <v>-9.18703626666667</v>
       </c>
       <c r="O83">
-        <v>-0.8088408086666682</v>
+        <v>-2.434564610666668</v>
       </c>
       <c r="P83">
-        <v>-2.243388658000004</v>
+        <v>-6.752471656000003</v>
       </c>
       <c r="Q83">
-        <v>2.196611341999997</v>
+        <v>-2.312471656000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1829511697935678</v>
+        <v>0.1987469821573525</v>
       </c>
       <c r="T83">
-        <v>3.167463505625124</v>
+        <v>3.532262867375347</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.2142748660670248</v>
+        <v>0.1547407672620359</v>
       </c>
       <c r="W83">
-        <v>0.1153444496613608</v>
+        <v>0.1697280539337832</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8085844002529236</v>
+        <v>0.5839274236303241</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1749514610140257</v>
+        <v>0.1765014610140257</v>
       </c>
       <c r="C84">
-        <v>-81.14040680898674</v>
+        <v>-82.79901205321286</v>
       </c>
       <c r="D84">
-        <v>26.78159319101327</v>
+        <v>26.46398794678714</v>
       </c>
       <c r="E84">
-        <v>56.962</v>
+        <v>58.30300000000001</v>
       </c>
       <c r="F84">
-        <v>109.962</v>
+        <v>111.303</v>
       </c>
       <c r="G84">
         <v>2.04</v>
@@ -8175,37 +8175,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M84">
-        <v>22.0803696</v>
+        <v>22.3496424</v>
       </c>
       <c r="N84">
-        <v>-9.18703626666667</v>
+        <v>-9.456309066666673</v>
       </c>
       <c r="O84">
-        <v>-2.434564610666668</v>
+        <v>-2.505921902666668</v>
       </c>
       <c r="P84">
-        <v>-6.752471656000003</v>
+        <v>-6.950387164000005</v>
       </c>
       <c r="Q84">
-        <v>-2.312471656000002</v>
+        <v>-2.510387164000004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1987469821573525</v>
+        <v>0.2077438634607262</v>
       </c>
       <c r="T84">
-        <v>3.532262867375347</v>
+        <v>3.740043036044486</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1547407672620359</v>
+        <v>0.1528764206685174</v>
       </c>
       <c r="W84">
-        <v>0.1697280539337832</v>
+        <v>0.1701024147297617</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5839274236303241</v>
+        <v>0.5768921534661033</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1765014610140257</v>
+        <v>0.1780514610140257</v>
       </c>
       <c r="C85">
-        <v>-82.79901205321286</v>
+        <v>-84.45017256866583</v>
       </c>
       <c r="D85">
-        <v>26.46398794678714</v>
+        <v>26.15382743133417</v>
       </c>
       <c r="E85">
-        <v>58.30300000000001</v>
+        <v>59.64400000000001</v>
       </c>
       <c r="F85">
-        <v>111.303</v>
+        <v>112.644</v>
       </c>
       <c r="G85">
         <v>2.04</v>
@@ -8257,37 +8257,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M85">
-        <v>22.3496424</v>
+        <v>22.6189152</v>
       </c>
       <c r="N85">
-        <v>-9.456309066666673</v>
+        <v>-9.725581866666673</v>
       </c>
       <c r="O85">
-        <v>-2.505921902666668</v>
+        <v>-2.577279194666668</v>
       </c>
       <c r="P85">
-        <v>-6.950387164000005</v>
+        <v>-7.148302672000004</v>
       </c>
       <c r="Q85">
-        <v>-2.510387164000004</v>
+        <v>-2.708302672000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2077438634607262</v>
+        <v>0.2178653549270216</v>
       </c>
       <c r="T85">
-        <v>3.740043036044486</v>
+        <v>3.973795725797266</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1528764206685174</v>
+        <v>0.1510564632796065</v>
       </c>
       <c r="W85">
-        <v>0.1701024147297617</v>
+        <v>0.170467862173455</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5768921534661033</v>
+        <v>0.570024389734364</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1780514610140257</v>
+        <v>0.1796014610140257</v>
       </c>
       <c r="C86">
-        <v>-84.45017256866582</v>
+        <v>-86.09414708188372</v>
       </c>
       <c r="D86">
-        <v>26.15382743133417</v>
+        <v>25.85085291811627</v>
       </c>
       <c r="E86">
-        <v>59.64399999999999</v>
+        <v>60.98499999999999</v>
       </c>
       <c r="F86">
-        <v>112.644</v>
+        <v>113.985</v>
       </c>
       <c r="G86">
         <v>2.04</v>
@@ -8339,37 +8339,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M86">
-        <v>22.6189152</v>
+        <v>22.888188</v>
       </c>
       <c r="N86">
-        <v>-9.725581866666669</v>
+        <v>-9.994854666666665</v>
       </c>
       <c r="O86">
-        <v>-2.577279194666668</v>
+        <v>-2.648636486666666</v>
       </c>
       <c r="P86">
-        <v>-7.148302672000002</v>
+        <v>-7.346218179999999</v>
       </c>
       <c r="Q86">
-        <v>-2.708302672000001</v>
+        <v>-2.906218179999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2178653549270215</v>
+        <v>0.2293363785888229</v>
       </c>
       <c r="T86">
-        <v>3.973795725797264</v>
+        <v>4.238715440850415</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1510564632796065</v>
+        <v>0.1492793284174935</v>
       </c>
       <c r="W86">
-        <v>0.170467862173455</v>
+        <v>0.1708247108537673</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.570024389734364</v>
+        <v>0.5633182204433717</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1796014610140257</v>
+        <v>0.1811514610140257</v>
       </c>
       <c r="C87">
-        <v>-86.09414708188372</v>
+        <v>-87.73118246800288</v>
       </c>
       <c r="D87">
-        <v>25.85085291811627</v>
+        <v>25.55481753199711</v>
       </c>
       <c r="E87">
-        <v>60.98499999999999</v>
+        <v>62.32599999999999</v>
       </c>
       <c r="F87">
-        <v>113.985</v>
+        <v>115.326</v>
       </c>
       <c r="G87">
         <v>2.04</v>
@@ -8421,37 +8421,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M87">
-        <v>22.888188</v>
+        <v>23.1574608</v>
       </c>
       <c r="N87">
-        <v>-9.994854666666665</v>
+        <v>-10.26412746666667</v>
       </c>
       <c r="O87">
-        <v>-2.648636486666666</v>
+        <v>-2.719993778666667</v>
       </c>
       <c r="P87">
-        <v>-7.346218179999999</v>
+        <v>-7.544133688000001</v>
       </c>
       <c r="Q87">
-        <v>-2.906218179999999</v>
+        <v>-3.104133688</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2293363785888229</v>
+        <v>0.242446119916596</v>
       </c>
       <c r="T87">
-        <v>4.238715440850415</v>
+        <v>4.541480829482587</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1492793284174935</v>
+        <v>0.147543522273104</v>
       </c>
       <c r="W87">
-        <v>0.1708247108537673</v>
+        <v>0.1711732607275607</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5633182204433717</v>
+        <v>0.5567680085777509</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1811514610140257</v>
+        <v>0.1827014610140257</v>
       </c>
       <c r="C88">
-        <v>-87.73118246800288</v>
+        <v>-89.36151442166654</v>
       </c>
       <c r="D88">
-        <v>25.55481753199711</v>
+        <v>25.26548557833345</v>
       </c>
       <c r="E88">
-        <v>62.32599999999999</v>
+        <v>63.66699999999999</v>
       </c>
       <c r="F88">
-        <v>115.326</v>
+        <v>116.667</v>
       </c>
       <c r="G88">
         <v>2.04</v>
@@ -8503,37 +8503,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M88">
-        <v>23.1574608</v>
+        <v>23.4267336</v>
       </c>
       <c r="N88">
-        <v>-10.26412746666667</v>
+        <v>-10.53340026666667</v>
       </c>
       <c r="O88">
-        <v>-2.719993778666667</v>
+        <v>-2.791351070666667</v>
       </c>
       <c r="P88">
-        <v>-7.544133688000001</v>
+        <v>-7.742049196000001</v>
       </c>
       <c r="Q88">
-        <v>-3.104133688</v>
+        <v>-3.302049196</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.242446119916596</v>
+        <v>0.2575727445255649</v>
       </c>
       <c r="T88">
-        <v>4.541480829482587</v>
+        <v>4.890825508673556</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.147543522273104</v>
+        <v>0.1458476197182407</v>
       </c>
       <c r="W88">
-        <v>0.1711732607275607</v>
+        <v>0.1715137979605773</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5567680085777509</v>
+        <v>0.550368376295248</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1827014610140257</v>
+        <v>0.1842514610140256</v>
       </c>
       <c r="C89">
-        <v>-89.36151442166654</v>
+        <v>-90.98536808286734</v>
       </c>
       <c r="D89">
-        <v>25.26548557833345</v>
+        <v>24.98263191713266</v>
       </c>
       <c r="E89">
-        <v>63.66699999999999</v>
+        <v>65.008</v>
       </c>
       <c r="F89">
-        <v>116.667</v>
+        <v>118.008</v>
       </c>
       <c r="G89">
         <v>2.04</v>
@@ -8585,37 +8585,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M89">
-        <v>23.4267336</v>
+        <v>23.6960064</v>
       </c>
       <c r="N89">
-        <v>-10.53340026666667</v>
+        <v>-10.80267306666667</v>
       </c>
       <c r="O89">
-        <v>-2.791351070666667</v>
+        <v>-2.862708362666667</v>
       </c>
       <c r="P89">
-        <v>-7.742049196000001</v>
+        <v>-7.939964704</v>
       </c>
       <c r="Q89">
-        <v>-3.302049196</v>
+        <v>-3.499964704</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2575727445255649</v>
+        <v>0.2752204732360287</v>
       </c>
       <c r="T89">
-        <v>4.890825508673556</v>
+        <v>5.298394301063019</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1458476197182407</v>
+        <v>0.1441902604032607</v>
       </c>
       <c r="W89">
-        <v>0.1715137979605773</v>
+        <v>0.1718465957110252</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.550368376295248</v>
+        <v>0.5441141902009838</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1842514610140256</v>
+        <v>0.1858014610140257</v>
       </c>
       <c r="C90">
-        <v>-90.98536808286734</v>
+        <v>-92.60295862121663</v>
       </c>
       <c r="D90">
-        <v>24.98263191713266</v>
+        <v>24.70604137878338</v>
       </c>
       <c r="E90">
-        <v>65.008</v>
+        <v>66.349</v>
       </c>
       <c r="F90">
-        <v>118.008</v>
+        <v>119.349</v>
       </c>
       <c r="G90">
         <v>2.04</v>
@@ -8667,37 +8667,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M90">
-        <v>23.6960064</v>
+        <v>23.9652792</v>
       </c>
       <c r="N90">
-        <v>-10.80267306666667</v>
+        <v>-11.07194586666667</v>
       </c>
       <c r="O90">
-        <v>-2.862708362666667</v>
+        <v>-2.934065654666668</v>
       </c>
       <c r="P90">
-        <v>-7.939964704</v>
+        <v>-8.137880212000002</v>
       </c>
       <c r="Q90">
-        <v>-3.499964704</v>
+        <v>-3.697880212000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2752204732360287</v>
+        <v>0.2960768798938495</v>
       </c>
       <c r="T90">
-        <v>5.298394301063019</v>
+        <v>5.780066510250567</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1441902604032607</v>
+        <v>0.1425701451178308</v>
       </c>
       <c r="W90">
-        <v>0.1718465957110252</v>
+        <v>0.1721719148603396</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5441141902009838</v>
+        <v>0.5380005476144559</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1858014610140257</v>
+        <v>0.1873514610140257</v>
       </c>
       <c r="C91">
-        <v>-92.60295862121663</v>
+        <v>-94.21449178182681</v>
       </c>
       <c r="D91">
-        <v>24.70604137878338</v>
+        <v>24.43550821817319</v>
       </c>
       <c r="E91">
-        <v>66.349</v>
+        <v>67.69</v>
       </c>
       <c r="F91">
-        <v>119.349</v>
+        <v>120.69</v>
       </c>
       <c r="G91">
         <v>2.04</v>
@@ -8749,37 +8749,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M91">
-        <v>23.9652792</v>
+        <v>24.234552</v>
       </c>
       <c r="N91">
-        <v>-11.07194586666667</v>
+        <v>-11.34121866666667</v>
       </c>
       <c r="O91">
-        <v>-2.934065654666668</v>
+        <v>-3.005422946666668</v>
       </c>
       <c r="P91">
-        <v>-8.137880212000002</v>
+        <v>-8.335795720000002</v>
       </c>
       <c r="Q91">
-        <v>-3.697880212000002</v>
+        <v>-3.895795720000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2960768798938495</v>
+        <v>0.3211045678832345</v>
       </c>
       <c r="T91">
-        <v>5.780066510250567</v>
+        <v>6.358073161275624</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1425701451178308</v>
+        <v>0.1409860323942994</v>
       </c>
       <c r="W91">
-        <v>0.1721719148603396</v>
+        <v>0.1724900046952247</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5380005476144559</v>
+        <v>0.5320227637520731</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1873514610140257</v>
+        <v>0.1889014610140256</v>
       </c>
       <c r="C92">
-        <v>-94.21449178182681</v>
+        <v>-95.82016439571757</v>
       </c>
       <c r="D92">
-        <v>24.43550821817319</v>
+        <v>24.17083560428244</v>
       </c>
       <c r="E92">
-        <v>67.69</v>
+        <v>69.03100000000001</v>
       </c>
       <c r="F92">
-        <v>120.69</v>
+        <v>122.031</v>
       </c>
       <c r="G92">
         <v>2.04</v>
@@ -8831,37 +8831,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M92">
-        <v>24.234552</v>
+        <v>24.5038248</v>
       </c>
       <c r="N92">
-        <v>-11.34121866666667</v>
+        <v>-11.61049146666667</v>
       </c>
       <c r="O92">
-        <v>-3.005422946666668</v>
+        <v>-3.076780238666668</v>
       </c>
       <c r="P92">
-        <v>-8.335795720000002</v>
+        <v>-8.533711228000001</v>
       </c>
       <c r="Q92">
-        <v>-3.895795720000002</v>
+        <v>-4.093711228000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3211045678832345</v>
+        <v>0.351693964314705</v>
       </c>
       <c r="T92">
-        <v>6.358073161275624</v>
+        <v>7.064525734750694</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1409860323942994</v>
+        <v>0.1394367353350214</v>
       </c>
       <c r="W92">
-        <v>0.1724900046952247</v>
+        <v>0.1728011035447277</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5320227637520731</v>
+        <v>0.5261763597547976</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1889014610140256</v>
+        <v>0.1904514610140257</v>
       </c>
       <c r="C93">
-        <v>-95.82016439571757</v>
+        <v>-97.42016485740669</v>
       </c>
       <c r="D93">
-        <v>24.17083560428244</v>
+        <v>23.91183514259331</v>
       </c>
       <c r="E93">
-        <v>69.03100000000001</v>
+        <v>70.372</v>
       </c>
       <c r="F93">
-        <v>122.031</v>
+        <v>123.372</v>
       </c>
       <c r="G93">
         <v>2.04</v>
@@ -8913,37 +8913,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M93">
-        <v>24.5038248</v>
+        <v>24.7730976</v>
       </c>
       <c r="N93">
-        <v>-11.61049146666667</v>
+        <v>-11.87976426666667</v>
       </c>
       <c r="O93">
-        <v>-3.076780238666668</v>
+        <v>-3.148137530666667</v>
       </c>
       <c r="P93">
-        <v>-8.533711228000001</v>
+        <v>-8.731626736000003</v>
       </c>
       <c r="Q93">
-        <v>-4.093711228000001</v>
+        <v>-4.291626736000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.351693964314705</v>
+        <v>0.3899307098540433</v>
       </c>
       <c r="T93">
-        <v>7.064525734750694</v>
+        <v>7.947591451594534</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1394367353350214</v>
+        <v>0.1379211186465972</v>
       </c>
       <c r="W93">
-        <v>0.1728011035447277</v>
+        <v>0.1731054393757633</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5261763597547976</v>
+        <v>0.5204570514965933</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1904514610140257</v>
+        <v>0.1920014610140257</v>
       </c>
       <c r="C94">
-        <v>-97.42016485740669</v>
+        <v>-99.01467357212101</v>
       </c>
       <c r="D94">
-        <v>23.91183514259331</v>
+        <v>23.658326427879</v>
       </c>
       <c r="E94">
-        <v>70.372</v>
+        <v>71.71300000000001</v>
       </c>
       <c r="F94">
-        <v>123.372</v>
+        <v>124.713</v>
       </c>
       <c r="G94">
         <v>2.04</v>
@@ -8995,37 +8995,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M94">
-        <v>24.7730976</v>
+        <v>25.0423704</v>
       </c>
       <c r="N94">
-        <v>-11.87976426666667</v>
+        <v>-12.14903706666667</v>
       </c>
       <c r="O94">
-        <v>-3.148137530666667</v>
+        <v>-3.219494822666668</v>
       </c>
       <c r="P94">
-        <v>-8.731626736000003</v>
+        <v>-8.929542244000004</v>
       </c>
       <c r="Q94">
-        <v>-4.291626736000002</v>
+        <v>-4.489542244000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3899307098540433</v>
+        <v>0.4390922398331923</v>
       </c>
       <c r="T94">
-        <v>7.947591451594534</v>
+        <v>9.082961658965182</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1379211186465972</v>
+        <v>0.136438095865451</v>
       </c>
       <c r="W94">
-        <v>0.1731054393757633</v>
+        <v>0.1734032303502175</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5204570514965933</v>
+        <v>0.5148607391149094</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1920014610140257</v>
+        <v>0.1935514610140257</v>
       </c>
       <c r="C95">
-        <v>-99.01467357212101</v>
+        <v>-100.6038633748582</v>
       </c>
       <c r="D95">
-        <v>23.658326427879</v>
+        <v>23.41013662514175</v>
       </c>
       <c r="E95">
-        <v>71.71300000000001</v>
+        <v>73.054</v>
       </c>
       <c r="F95">
-        <v>124.713</v>
+        <v>126.054</v>
       </c>
       <c r="G95">
         <v>2.04</v>
@@ -9077,37 +9077,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M95">
-        <v>25.0423704</v>
+        <v>25.3116432</v>
       </c>
       <c r="N95">
-        <v>-12.14903706666667</v>
+        <v>-12.41830986666667</v>
       </c>
       <c r="O95">
-        <v>-3.219494822666668</v>
+        <v>-3.290852114666668</v>
       </c>
       <c r="P95">
-        <v>-8.929542244000004</v>
+        <v>-9.127457752000003</v>
       </c>
       <c r="Q95">
-        <v>-4.489542244000003</v>
+        <v>-4.687457752000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4390922398331923</v>
+        <v>0.5046409464720578</v>
       </c>
       <c r="T95">
-        <v>9.082961658965182</v>
+        <v>10.59678860212605</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.136438095865451</v>
+        <v>0.1349866267604994</v>
       </c>
       <c r="W95">
-        <v>0.1734032303502175</v>
+        <v>0.1736946853464917</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5148607391149094</v>
+        <v>0.5093834972094317</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1935514610140257</v>
+        <v>0.1951014610140257</v>
       </c>
       <c r="C96">
-        <v>-100.6038633748582</v>
+        <v>-102.1878999233456</v>
       </c>
       <c r="D96">
-        <v>23.41013662514175</v>
+        <v>23.16710007665438</v>
       </c>
       <c r="E96">
-        <v>73.054</v>
+        <v>74.39500000000001</v>
       </c>
       <c r="F96">
-        <v>126.054</v>
+        <v>127.395</v>
       </c>
       <c r="G96">
         <v>2.04</v>
@@ -9159,37 +9159,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M96">
-        <v>25.3116432</v>
+        <v>25.580916</v>
       </c>
       <c r="N96">
-        <v>-12.41830986666667</v>
+        <v>-12.68758266666667</v>
       </c>
       <c r="O96">
-        <v>-3.290852114666668</v>
+        <v>-3.362209406666668</v>
       </c>
       <c r="P96">
-        <v>-9.127457752000003</v>
+        <v>-9.325373260000003</v>
       </c>
       <c r="Q96">
-        <v>-4.687457752000003</v>
+        <v>-4.885373260000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5046409464720578</v>
+        <v>0.5964091357664696</v>
       </c>
       <c r="T96">
-        <v>10.59678860212605</v>
+        <v>12.71614632255126</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1349866267604994</v>
+        <v>0.1335657148998625</v>
       </c>
       <c r="W96">
-        <v>0.1736946853464917</v>
+        <v>0.1739800044481076</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5093834972094317</v>
+        <v>0.5040215656598587</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1951014610140257</v>
+        <v>0.230845323672472</v>
       </c>
       <c r="C97">
-        <v>-102.1878999233456</v>
+        <v>-108.0039205663969</v>
       </c>
       <c r="D97">
-        <v>23.16710007665438</v>
+        <v>18.69207943360311</v>
       </c>
       <c r="E97">
-        <v>74.39500000000001</v>
+        <v>75.73600000000002</v>
       </c>
       <c r="F97">
-        <v>127.395</v>
+        <v>128.736</v>
       </c>
       <c r="G97">
         <v>2.04</v>
@@ -9241,45 +9241,45 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M97">
-        <v>25.580916</v>
+        <v>30.35594880000001</v>
       </c>
       <c r="N97">
-        <v>-12.68758266666667</v>
+        <v>-17.46261546666668</v>
       </c>
       <c r="O97">
-        <v>-3.362209406666668</v>
+        <v>-4.62759309866667</v>
       </c>
       <c r="P97">
-        <v>-9.325373260000003</v>
+        <v>-12.83502236800001</v>
       </c>
       <c r="Q97">
-        <v>-4.885373260000002</v>
+        <v>-8.395022368000006</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5964091357664696</v>
+        <v>0.748907986169246</v>
       </c>
       <c r="T97">
-        <v>12.71614632255126</v>
+        <v>16.23805972677243</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1335657148998625</v>
+        <v>0.1125556429102072</v>
       </c>
       <c r="W97">
-        <v>0.1739800044481076</v>
+        <v>0.2092593794017732</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5040215656598587</v>
+        <v>0.4247382751328572</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.230845323672472</v>
+        <v>0.232745323672472</v>
       </c>
       <c r="C98">
-        <v>-108.0039205663969</v>
+        <v>-109.5348956362524</v>
       </c>
       <c r="D98">
-        <v>18.69207943360311</v>
+        <v>18.50210436374757</v>
       </c>
       <c r="E98">
-        <v>75.73599999999999</v>
+        <v>77.077</v>
       </c>
       <c r="F98">
-        <v>128.736</v>
+        <v>130.077</v>
       </c>
       <c r="G98">
         <v>2.04</v>
@@ -9323,37 +9323,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M98">
-        <v>30.3559488</v>
+        <v>30.6721566</v>
       </c>
       <c r="N98">
-        <v>-17.46261546666667</v>
+        <v>-17.77882326666667</v>
       </c>
       <c r="O98">
-        <v>-4.627593098666668</v>
+        <v>-4.711388165666667</v>
       </c>
       <c r="P98">
-        <v>-12.835022368</v>
+        <v>-13.067435101</v>
       </c>
       <c r="Q98">
-        <v>-8.395022367999999</v>
+        <v>-8.627435101000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7489079861692443</v>
+        <v>0.9832773148923257</v>
       </c>
       <c r="T98">
-        <v>16.23805972677239</v>
+        <v>21.65074630236318</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1125556429102072</v>
+        <v>0.1113952754575246</v>
       </c>
       <c r="W98">
-        <v>0.2092593794017731</v>
+        <v>0.2095329940471157</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4247382751328573</v>
+        <v>0.4203595300283949</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.232745323672472</v>
+        <v>0.234645323672472</v>
       </c>
       <c r="C99">
-        <v>-109.5348956362524</v>
+        <v>-111.0620479730298</v>
       </c>
       <c r="D99">
-        <v>18.50210436374757</v>
+        <v>18.31595202697013</v>
       </c>
       <c r="E99">
-        <v>77.077</v>
+        <v>78.41799999999998</v>
       </c>
       <c r="F99">
-        <v>130.077</v>
+        <v>131.418</v>
       </c>
       <c r="G99">
         <v>2.04</v>
@@ -9405,37 +9405,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M99">
-        <v>30.6721566</v>
+        <v>30.98836439999999</v>
       </c>
       <c r="N99">
-        <v>-17.77882326666667</v>
+        <v>-18.09503106666666</v>
       </c>
       <c r="O99">
-        <v>-4.711388165666667</v>
+        <v>-4.795183232666666</v>
       </c>
       <c r="P99">
-        <v>-13.067435101</v>
+        <v>-13.299847834</v>
       </c>
       <c r="Q99">
-        <v>-8.627435101000003</v>
+        <v>-8.859847833999996</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9832773148923257</v>
+        <v>1.452015972338489</v>
       </c>
       <c r="T99">
-        <v>21.65074630236318</v>
+        <v>32.47611945354478</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1113952754575246</v>
+        <v>0.1102585889732642</v>
       </c>
       <c r="W99">
-        <v>0.2095329940471157</v>
+        <v>0.2098010247201043</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4203595300283949</v>
+        <v>0.4160701470689215</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.234645323672472</v>
+        <v>0.236545323672472</v>
       </c>
       <c r="C100">
-        <v>-111.0620479730298</v>
+        <v>-112.5854918106098</v>
       </c>
       <c r="D100">
-        <v>18.31595202697013</v>
+        <v>18.13350818939015</v>
       </c>
       <c r="E100">
-        <v>78.41799999999998</v>
+        <v>79.75899999999999</v>
       </c>
       <c r="F100">
-        <v>131.418</v>
+        <v>132.759</v>
       </c>
       <c r="G100">
         <v>2.04</v>
@@ -9487,37 +9487,37 @@
         <v>12.89333333333333</v>
       </c>
       <c r="M100">
-        <v>30.98836439999999</v>
+        <v>31.3045722</v>
       </c>
       <c r="N100">
-        <v>-18.09503106666666</v>
+        <v>-18.41123886666667</v>
       </c>
       <c r="O100">
-        <v>-4.795183232666666</v>
+        <v>-4.878978299666668</v>
       </c>
       <c r="P100">
-        <v>-13.299847834</v>
+        <v>-13.532260567</v>
       </c>
       <c r="Q100">
-        <v>-8.859847833999996</v>
+        <v>-9.092260567</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.452015972338489</v>
+        <v>2.858231944676977</v>
       </c>
       <c r="T100">
-        <v>32.47611945354478</v>
+        <v>64.95223890708955</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1102585889732642</v>
+        <v>0.1091448658523221</v>
       </c>
       <c r="W100">
-        <v>0.2098010247201043</v>
+        <v>0.2100636406320224</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4160701470689215</v>
+        <v>0.4118674183106495</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.236545323672472</v>
-      </c>
-      <c r="C101">
-        <v>-112.5854918106098</v>
-      </c>
-      <c r="D101">
-        <v>18.13350818939015</v>
-      </c>
-      <c r="E101">
-        <v>79.75899999999999</v>
-      </c>
-      <c r="F101">
-        <v>132.759</v>
-      </c>
-      <c r="G101">
-        <v>2.04</v>
-      </c>
-      <c r="H101">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.33333333333333</v>
-      </c>
-      <c r="K101">
-        <v>4.44</v>
-      </c>
-      <c r="L101">
-        <v>12.89333333333333</v>
-      </c>
-      <c r="M101">
-        <v>31.3045722</v>
-      </c>
-      <c r="N101">
-        <v>-18.41123886666667</v>
-      </c>
-      <c r="O101">
-        <v>-4.878978299666668</v>
-      </c>
-      <c r="P101">
-        <v>-13.532260567</v>
-      </c>
-      <c r="Q101">
-        <v>-9.092260567</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.858231944676977</v>
-      </c>
-      <c r="T101">
-        <v>64.95223890708955</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1091448658523221</v>
-      </c>
-      <c r="W101">
-        <v>0.2100636406320224</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4118674183106495</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
